--- a/.raw/易畫165與ASCII94.xlsx
+++ b/.raw/易畫165與ASCII94.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\share\git\rime-jek\.trash\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="B:\share\git\public\rime-jek\.raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90AEE651-A2CA-480F-9CBD-39BBBFC30110}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A17DFC1-2379-49C3-9320-6EAD777BAA90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="9" xr2:uid="{B55F1E0F-6405-49D3-ACBC-C1F7C0B264EC}"/>
   </bookViews>
@@ -9111,13 +9111,13 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{364783B0-24A1-40F6-AA0A-4F4A38EFD675}">
-  <dimension ref="A1:P166"/>
+  <dimension ref="A1:R166"/>
   <sheetFormatPr defaultRowHeight="16.2"/>
   <cols>
     <col min="12" max="12" width="10.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:18">
       <c r="A1" t="s">
         <v>5</v>
       </c>
@@ -9134,7 +9134,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:16">
+    <row r="2" spans="1:18">
       <c r="A2">
         <v>2630</v>
       </c>
@@ -9179,7 +9179,7 @@
         <v>⚊⚊⚊</v>
       </c>
       <c r="M2" t="str">
-        <f t="shared" ref="M2:P17" si="0">_xlfn.UNICHAR($C2)</f>
+        <f t="shared" ref="M2:M17" si="0">_xlfn.UNICHAR($C2)</f>
         <v>☰</v>
       </c>
       <c r="N2" t="str">
@@ -9191,11 +9191,19 @@
         <v>☰天</v>
       </c>
       <c r="P2" t="str">
-        <f t="shared" si="0"/>
-        <v>☰</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+        <f>_xlfn.UNICHAR($C2)&amp;"p"</f>
+        <v>☰p</v>
+      </c>
+      <c r="Q2" t="str">
+        <f>"&lt;ruby&gt;"&amp;$M2&amp;"&lt;rt&gt;&amp;#x202E;"&amp;$N2&amp;"&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;"</f>
+        <v>&lt;ruby&gt;☰&lt;rt&gt;&amp;#x202E;天&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R2" t="str">
+        <f>_xlfn.UNICHAR($C2)&amp;"q"</f>
+        <v>☰q</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18">
       <c r="B3" t="str">
         <f t="shared" ref="B3:B66" si="1">DEC2HEX($C3)</f>
         <v>2631</v>
@@ -9249,11 +9257,19 @@
         <v>☱澤</v>
       </c>
       <c r="P3" t="str">
-        <f t="shared" si="0"/>
-        <v>☱</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
+        <f t="shared" ref="P3:P66" si="5">_xlfn.UNICHAR($C3)&amp;"p"</f>
+        <v>☱p</v>
+      </c>
+      <c r="Q3" t="str">
+        <f t="shared" ref="Q3:Q66" si="6">"&lt;ruby&gt;"&amp;$M3&amp;"&lt;rt&gt;&amp;#x202E;"&amp;$N3&amp;"&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;"</f>
+        <v>&lt;ruby&gt;☱&lt;rt&gt;&amp;#x202E;澤&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R3" t="str">
+        <f t="shared" ref="R3:R66" si="7">_xlfn.UNICHAR($C3)&amp;"q"</f>
+        <v>☱q</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18">
       <c r="B4" t="str">
         <f t="shared" si="1"/>
         <v>2632</v>
@@ -9269,7 +9285,7 @@
         <v>3</v>
       </c>
       <c r="F4" t="str">
-        <f t="shared" ref="F4:F166" si="5">_xlfn.UNICHAR($C4)</f>
+        <f t="shared" ref="F4:F166" si="8">_xlfn.UNICHAR($C4)</f>
         <v>☲</v>
       </c>
       <c r="G4" t="s">
@@ -9307,11 +9323,19 @@
         <v>☲火</v>
       </c>
       <c r="P4" t="str">
-        <f t="shared" si="0"/>
-        <v>☲</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>☲p</v>
+      </c>
+      <c r="Q4" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;☲&lt;rt&gt;&amp;#x202E;火&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R4" t="str">
+        <f t="shared" si="7"/>
+        <v>☲q</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18">
       <c r="B5" t="str">
         <f t="shared" si="1"/>
         <v>2633</v>
@@ -9327,7 +9351,7 @@
         <v>4</v>
       </c>
       <c r="F5" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>☳</v>
       </c>
       <c r="G5" t="s">
@@ -9365,11 +9389,19 @@
         <v>☳雷</v>
       </c>
       <c r="P5" t="str">
-        <f t="shared" si="0"/>
-        <v>☳</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>☳p</v>
+      </c>
+      <c r="Q5" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;☳&lt;rt&gt;&amp;#x202E;雷&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R5" t="str">
+        <f t="shared" si="7"/>
+        <v>☳q</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18">
       <c r="B6" t="str">
         <f t="shared" si="1"/>
         <v>2634</v>
@@ -9385,7 +9417,7 @@
         <v>5</v>
       </c>
       <c r="F6" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>☴</v>
       </c>
       <c r="G6" t="s">
@@ -9423,11 +9455,19 @@
         <v>☴風</v>
       </c>
       <c r="P6" t="str">
-        <f t="shared" si="0"/>
-        <v>☴</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>☴p</v>
+      </c>
+      <c r="Q6" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;☴&lt;rt&gt;&amp;#x202E;風&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R6" t="str">
+        <f t="shared" si="7"/>
+        <v>☴q</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18">
       <c r="B7" t="str">
         <f t="shared" si="1"/>
         <v>2635</v>
@@ -9443,7 +9483,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>☵</v>
       </c>
       <c r="G7" t="s">
@@ -9481,11 +9521,19 @@
         <v>☵水</v>
       </c>
       <c r="P7" t="str">
-        <f t="shared" si="0"/>
-        <v>☵</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>☵p</v>
+      </c>
+      <c r="Q7" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;☵&lt;rt&gt;&amp;#x202E;水&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R7" t="str">
+        <f t="shared" si="7"/>
+        <v>☵q</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18">
       <c r="B8" t="str">
         <f t="shared" si="1"/>
         <v>2636</v>
@@ -9501,7 +9549,7 @@
         <v>7</v>
       </c>
       <c r="F8" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>☶</v>
       </c>
       <c r="G8" t="s">
@@ -9539,11 +9587,19 @@
         <v>☶山</v>
       </c>
       <c r="P8" t="str">
-        <f t="shared" si="0"/>
-        <v>☶</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>☶p</v>
+      </c>
+      <c r="Q8" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;☶&lt;rt&gt;&amp;#x202E;山&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R8" t="str">
+        <f t="shared" si="7"/>
+        <v>☶q</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18">
       <c r="B9" t="str">
         <f t="shared" si="1"/>
         <v>2637</v>
@@ -9559,7 +9615,7 @@
         <v>8</v>
       </c>
       <c r="F9" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>☷</v>
       </c>
       <c r="G9" t="s">
@@ -9596,11 +9652,19 @@
         <v>☷地</v>
       </c>
       <c r="P9" t="str">
-        <f t="shared" si="0"/>
-        <v>☷</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>☷p</v>
+      </c>
+      <c r="Q9" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;☷&lt;rt&gt;&amp;#x202E;地&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R9" t="str">
+        <f t="shared" si="7"/>
+        <v>☷q</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -9619,7 +9683,7 @@
         <v>1</v>
       </c>
       <c r="F10" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>⚊</v>
       </c>
       <c r="G10" t="s">
@@ -9656,11 +9720,19 @@
         <v>⚊陽</v>
       </c>
       <c r="P10" t="str">
-        <f t="shared" si="0"/>
-        <v>⚊</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>⚊p</v>
+      </c>
+      <c r="Q10" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;⚊&lt;rt&gt;&amp;#x202E;陽&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R10" t="str">
+        <f t="shared" si="7"/>
+        <v>⚊q</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18">
       <c r="B11" t="str">
         <f t="shared" si="1"/>
         <v>268B</v>
@@ -9676,7 +9748,7 @@
         <v>2</v>
       </c>
       <c r="F11" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>⚋</v>
       </c>
       <c r="G11" t="s">
@@ -9713,11 +9785,19 @@
         <v>⚋陰</v>
       </c>
       <c r="P11" t="str">
-        <f t="shared" si="0"/>
-        <v>⚋</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>⚋p</v>
+      </c>
+      <c r="Q11" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;⚋&lt;rt&gt;&amp;#x202E;陰&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R11" t="str">
+        <f t="shared" si="7"/>
+        <v>⚋q</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
       <c r="B12" t="str">
         <f t="shared" si="1"/>
         <v>268C</v>
@@ -9733,7 +9813,7 @@
         <v>1</v>
       </c>
       <c r="F12" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>⚌</v>
       </c>
       <c r="G12" t="s">
@@ -9768,11 +9848,19 @@
         <v>⚌老陽</v>
       </c>
       <c r="P12" t="str">
-        <f t="shared" si="0"/>
-        <v>⚌</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>⚌p</v>
+      </c>
+      <c r="Q12" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;⚌&lt;rt&gt;&amp;#x202E;老陽&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R12" t="str">
+        <f t="shared" si="7"/>
+        <v>⚌q</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18">
       <c r="B13" t="str">
         <f t="shared" si="1"/>
         <v>268D</v>
@@ -9788,7 +9876,7 @@
         <v>2</v>
       </c>
       <c r="F13" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>⚍</v>
       </c>
       <c r="G13" t="s">
@@ -9823,11 +9911,19 @@
         <v>⚍少陰</v>
       </c>
       <c r="P13" t="str">
-        <f t="shared" si="0"/>
-        <v>⚍</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>⚍p</v>
+      </c>
+      <c r="Q13" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;⚍&lt;rt&gt;&amp;#x202E;少陰&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R13" t="str">
+        <f t="shared" si="7"/>
+        <v>⚍q</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18">
       <c r="B14" t="str">
         <f t="shared" si="1"/>
         <v>268E</v>
@@ -9843,7 +9939,7 @@
         <v>3</v>
       </c>
       <c r="F14" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>⚎</v>
       </c>
       <c r="G14" t="s">
@@ -9878,11 +9974,19 @@
         <v>⚎少陽</v>
       </c>
       <c r="P14" t="str">
-        <f t="shared" si="0"/>
-        <v>⚎</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>⚎p</v>
+      </c>
+      <c r="Q14" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;⚎&lt;rt&gt;&amp;#x202E;少陽&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R14" t="str">
+        <f t="shared" si="7"/>
+        <v>⚎q</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
       <c r="B15" t="str">
         <f t="shared" si="1"/>
         <v>268F</v>
@@ -9898,7 +10002,7 @@
         <v>4</v>
       </c>
       <c r="F15" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>⚏</v>
       </c>
       <c r="G15" t="s">
@@ -9933,11 +10037,19 @@
         <v>⚏老陰</v>
       </c>
       <c r="P15" t="str">
-        <f t="shared" si="0"/>
-        <v>⚏</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>⚏p</v>
+      </c>
+      <c r="Q15" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;⚏&lt;rt&gt;&amp;#x202E;老陰&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R15" t="str">
+        <f t="shared" si="7"/>
+        <v>⚏q</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18">
       <c r="A16" t="s">
         <v>3</v>
       </c>
@@ -9956,7 +10068,7 @@
         <v>1</v>
       </c>
       <c r="F16" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷀</v>
       </c>
       <c r="G16" t="s">
@@ -9991,11 +10103,19 @@
         <v>䷀乾</v>
       </c>
       <c r="P16" t="str">
-        <f t="shared" si="0"/>
-        <v>䷀</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷀p</v>
+      </c>
+      <c r="Q16" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷀&lt;rt&gt;&amp;#x202E;乾&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R16" t="str">
+        <f t="shared" si="7"/>
+        <v>䷀q</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18">
       <c r="B17" t="str">
         <f t="shared" si="1"/>
         <v>4DC1</v>
@@ -10011,7 +10131,7 @@
         <v>2</v>
       </c>
       <c r="F17" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷁</v>
       </c>
       <c r="G17" t="s">
@@ -10046,11 +10166,19 @@
         <v>䷁坤</v>
       </c>
       <c r="P17" t="str">
-        <f t="shared" si="0"/>
-        <v>䷁</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷁p</v>
+      </c>
+      <c r="Q17" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷁&lt;rt&gt;&amp;#x202E;坤&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R17" t="str">
+        <f t="shared" si="7"/>
+        <v>䷁q</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18">
       <c r="B18" t="str">
         <f t="shared" si="1"/>
         <v>4DC2</v>
@@ -10066,7 +10194,7 @@
         <v>3</v>
       </c>
       <c r="F18" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷂</v>
       </c>
       <c r="G18" t="s">
@@ -10089,7 +10217,7 @@
         <v>⚋⚊⚋⚋⚋⚊</v>
       </c>
       <c r="M18" t="str">
-        <f t="shared" ref="M18:P33" si="6">_xlfn.UNICHAR($C18)</f>
+        <f t="shared" ref="M18:M33" si="9">_xlfn.UNICHAR($C18)</f>
         <v>䷂</v>
       </c>
       <c r="N18" t="str">
@@ -10101,11 +10229,19 @@
         <v>䷂屯</v>
       </c>
       <c r="P18" t="str">
+        <f t="shared" si="5"/>
+        <v>䷂p</v>
+      </c>
+      <c r="Q18" t="str">
         <f t="shared" si="6"/>
-        <v>䷂</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16">
+        <v>&lt;ruby&gt;䷂&lt;rt&gt;&amp;#x202E;屯&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R18" t="str">
+        <f t="shared" si="7"/>
+        <v>䷂q</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18">
       <c r="B19" t="str">
         <f t="shared" si="1"/>
         <v>4DC3</v>
@@ -10121,7 +10257,7 @@
         <v>4</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷃</v>
       </c>
       <c r="G19" t="s">
@@ -10144,7 +10280,7 @@
         <v>⚊⚋⚋⚋⚊⚋</v>
       </c>
       <c r="M19" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷃</v>
       </c>
       <c r="N19" t="str">
@@ -10156,11 +10292,19 @@
         <v>䷃蒙</v>
       </c>
       <c r="P19" t="str">
+        <f t="shared" si="5"/>
+        <v>䷃p</v>
+      </c>
+      <c r="Q19" t="str">
         <f t="shared" si="6"/>
-        <v>䷃</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16">
+        <v>&lt;ruby&gt;䷃&lt;rt&gt;&amp;#x202E;蒙&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R19" t="str">
+        <f t="shared" si="7"/>
+        <v>䷃q</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18">
       <c r="B20" t="str">
         <f t="shared" si="1"/>
         <v>4DC4</v>
@@ -10176,7 +10320,7 @@
         <v>5</v>
       </c>
       <c r="F20" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷄</v>
       </c>
       <c r="G20" t="s">
@@ -10199,7 +10343,7 @@
         <v>⚋⚊⚋⚊⚊⚊</v>
       </c>
       <c r="M20" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷄</v>
       </c>
       <c r="N20" t="str">
@@ -10211,11 +10355,19 @@
         <v>䷄需</v>
       </c>
       <c r="P20" t="str">
+        <f t="shared" si="5"/>
+        <v>䷄p</v>
+      </c>
+      <c r="Q20" t="str">
         <f t="shared" si="6"/>
-        <v>䷄</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16">
+        <v>&lt;ruby&gt;䷄&lt;rt&gt;&amp;#x202E;需&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R20" t="str">
+        <f t="shared" si="7"/>
+        <v>䷄q</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18">
       <c r="B21" t="str">
         <f t="shared" si="1"/>
         <v>4DC5</v>
@@ -10231,7 +10383,7 @@
         <v>6</v>
       </c>
       <c r="F21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷅</v>
       </c>
       <c r="G21" t="s">
@@ -10254,7 +10406,7 @@
         <v>⚊⚊⚊⚋⚊⚋</v>
       </c>
       <c r="M21" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷅</v>
       </c>
       <c r="N21" t="str">
@@ -10266,11 +10418,19 @@
         <v>䷅訟</v>
       </c>
       <c r="P21" t="str">
+        <f t="shared" si="5"/>
+        <v>䷅p</v>
+      </c>
+      <c r="Q21" t="str">
         <f t="shared" si="6"/>
-        <v>䷅</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16">
+        <v>&lt;ruby&gt;䷅&lt;rt&gt;&amp;#x202E;訟&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R21" t="str">
+        <f t="shared" si="7"/>
+        <v>䷅q</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18">
       <c r="B22" t="str">
         <f t="shared" si="1"/>
         <v>4DC6</v>
@@ -10286,7 +10446,7 @@
         <v>7</v>
       </c>
       <c r="F22" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷆</v>
       </c>
       <c r="G22" t="s">
@@ -10309,7 +10469,7 @@
         <v>⚋⚋⚋⚋⚊⚋</v>
       </c>
       <c r="M22" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷆</v>
       </c>
       <c r="N22" t="str">
@@ -10321,11 +10481,19 @@
         <v>䷆師</v>
       </c>
       <c r="P22" t="str">
+        <f t="shared" si="5"/>
+        <v>䷆p</v>
+      </c>
+      <c r="Q22" t="str">
         <f t="shared" si="6"/>
-        <v>䷆</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16">
+        <v>&lt;ruby&gt;䷆&lt;rt&gt;&amp;#x202E;師&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R22" t="str">
+        <f t="shared" si="7"/>
+        <v>䷆q</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18">
       <c r="B23" t="str">
         <f t="shared" si="1"/>
         <v>4DC7</v>
@@ -10341,7 +10509,7 @@
         <v>8</v>
       </c>
       <c r="F23" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷇</v>
       </c>
       <c r="G23" t="s">
@@ -10364,7 +10532,7 @@
         <v>⚋⚊⚋⚋⚋⚋</v>
       </c>
       <c r="M23" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷇</v>
       </c>
       <c r="N23" t="str">
@@ -10376,11 +10544,19 @@
         <v>䷇比</v>
       </c>
       <c r="P23" t="str">
+        <f t="shared" si="5"/>
+        <v>䷇p</v>
+      </c>
+      <c r="Q23" t="str">
         <f t="shared" si="6"/>
-        <v>䷇</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16">
+        <v>&lt;ruby&gt;䷇&lt;rt&gt;&amp;#x202E;比&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R23" t="str">
+        <f t="shared" si="7"/>
+        <v>䷇q</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18">
       <c r="B24" t="str">
         <f t="shared" si="1"/>
         <v>4DC8</v>
@@ -10396,7 +10572,7 @@
         <v>9</v>
       </c>
       <c r="F24" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷈</v>
       </c>
       <c r="G24" t="s">
@@ -10419,7 +10595,7 @@
         <v>⚊⚊⚋⚊⚊⚊</v>
       </c>
       <c r="M24" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷈</v>
       </c>
       <c r="N24" t="str">
@@ -10431,11 +10607,19 @@
         <v>䷈小畜</v>
       </c>
       <c r="P24" t="str">
+        <f t="shared" si="5"/>
+        <v>䷈p</v>
+      </c>
+      <c r="Q24" t="str">
         <f t="shared" si="6"/>
-        <v>䷈</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16">
+        <v>&lt;ruby&gt;䷈&lt;rt&gt;&amp;#x202E;小畜&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R24" t="str">
+        <f t="shared" si="7"/>
+        <v>䷈q</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18">
       <c r="B25" t="str">
         <f t="shared" si="1"/>
         <v>4DC9</v>
@@ -10451,7 +10635,7 @@
         <v>10</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷉</v>
       </c>
       <c r="G25" t="s">
@@ -10474,7 +10658,7 @@
         <v>⚊⚊⚊⚋⚊⚊</v>
       </c>
       <c r="M25" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷉</v>
       </c>
       <c r="N25" t="str">
@@ -10486,11 +10670,19 @@
         <v>䷉履</v>
       </c>
       <c r="P25" t="str">
+        <f t="shared" si="5"/>
+        <v>䷉p</v>
+      </c>
+      <c r="Q25" t="str">
         <f t="shared" si="6"/>
-        <v>䷉</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16">
+        <v>&lt;ruby&gt;䷉&lt;rt&gt;&amp;#x202E;履&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R25" t="str">
+        <f t="shared" si="7"/>
+        <v>䷉q</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18">
       <c r="B26" t="str">
         <f t="shared" si="1"/>
         <v>4DCA</v>
@@ -10506,7 +10698,7 @@
         <v>11</v>
       </c>
       <c r="F26" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷊</v>
       </c>
       <c r="G26" t="s">
@@ -10529,7 +10721,7 @@
         <v>⚋⚋⚋⚊⚊⚊</v>
       </c>
       <c r="M26" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷊</v>
       </c>
       <c r="N26" t="str">
@@ -10541,11 +10733,19 @@
         <v>䷊泰</v>
       </c>
       <c r="P26" t="str">
+        <f t="shared" si="5"/>
+        <v>䷊p</v>
+      </c>
+      <c r="Q26" t="str">
         <f t="shared" si="6"/>
-        <v>䷊</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16">
+        <v>&lt;ruby&gt;䷊&lt;rt&gt;&amp;#x202E;泰&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R26" t="str">
+        <f t="shared" si="7"/>
+        <v>䷊q</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18">
       <c r="B27" t="str">
         <f t="shared" si="1"/>
         <v>4DCB</v>
@@ -10561,7 +10761,7 @@
         <v>12</v>
       </c>
       <c r="F27" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷋</v>
       </c>
       <c r="G27" t="s">
@@ -10584,7 +10784,7 @@
         <v>⚊⚊⚊⚋⚋⚋</v>
       </c>
       <c r="M27" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷋</v>
       </c>
       <c r="N27" t="str">
@@ -10596,11 +10796,19 @@
         <v>䷋否</v>
       </c>
       <c r="P27" t="str">
+        <f t="shared" si="5"/>
+        <v>䷋p</v>
+      </c>
+      <c r="Q27" t="str">
         <f t="shared" si="6"/>
-        <v>䷋</v>
-      </c>
-    </row>
-    <row r="28" spans="2:16">
+        <v>&lt;ruby&gt;䷋&lt;rt&gt;&amp;#x202E;否&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R27" t="str">
+        <f t="shared" si="7"/>
+        <v>䷋q</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18">
       <c r="B28" t="str">
         <f t="shared" si="1"/>
         <v>4DCC</v>
@@ -10616,7 +10824,7 @@
         <v>13</v>
       </c>
       <c r="F28" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷌</v>
       </c>
       <c r="G28" t="s">
@@ -10639,7 +10847,7 @@
         <v>⚊⚊⚊⚊⚋⚊</v>
       </c>
       <c r="M28" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷌</v>
       </c>
       <c r="N28" t="str">
@@ -10651,11 +10859,19 @@
         <v>䷌同人</v>
       </c>
       <c r="P28" t="str">
+        <f t="shared" si="5"/>
+        <v>䷌p</v>
+      </c>
+      <c r="Q28" t="str">
         <f t="shared" si="6"/>
-        <v>䷌</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16">
+        <v>&lt;ruby&gt;䷌&lt;rt&gt;&amp;#x202E;同人&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R28" t="str">
+        <f t="shared" si="7"/>
+        <v>䷌q</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18">
       <c r="B29" t="str">
         <f t="shared" si="1"/>
         <v>4DCD</v>
@@ -10671,7 +10887,7 @@
         <v>14</v>
       </c>
       <c r="F29" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷍</v>
       </c>
       <c r="G29" t="s">
@@ -10694,7 +10910,7 @@
         <v>⚊⚋⚊⚊⚊⚊</v>
       </c>
       <c r="M29" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷍</v>
       </c>
       <c r="N29" t="str">
@@ -10706,11 +10922,19 @@
         <v>䷍大有</v>
       </c>
       <c r="P29" t="str">
+        <f t="shared" si="5"/>
+        <v>䷍p</v>
+      </c>
+      <c r="Q29" t="str">
         <f t="shared" si="6"/>
-        <v>䷍</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16">
+        <v>&lt;ruby&gt;䷍&lt;rt&gt;&amp;#x202E;大有&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R29" t="str">
+        <f t="shared" si="7"/>
+        <v>䷍q</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18">
       <c r="B30" t="str">
         <f t="shared" si="1"/>
         <v>4DCE</v>
@@ -10726,7 +10950,7 @@
         <v>15</v>
       </c>
       <c r="F30" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷎</v>
       </c>
       <c r="G30" t="s">
@@ -10749,7 +10973,7 @@
         <v>⚋⚋⚋⚊⚋⚋</v>
       </c>
       <c r="M30" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷎</v>
       </c>
       <c r="N30" t="str">
@@ -10761,11 +10985,19 @@
         <v>䷎謙</v>
       </c>
       <c r="P30" t="str">
+        <f t="shared" si="5"/>
+        <v>䷎p</v>
+      </c>
+      <c r="Q30" t="str">
         <f t="shared" si="6"/>
-        <v>䷎</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16">
+        <v>&lt;ruby&gt;䷎&lt;rt&gt;&amp;#x202E;謙&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R30" t="str">
+        <f t="shared" si="7"/>
+        <v>䷎q</v>
+      </c>
+    </row>
+    <row r="31" spans="2:18">
       <c r="B31" t="str">
         <f t="shared" si="1"/>
         <v>4DCF</v>
@@ -10781,7 +11013,7 @@
         <v>16</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷏</v>
       </c>
       <c r="G31" t="s">
@@ -10804,7 +11036,7 @@
         <v>⚋⚋⚊⚋⚋⚋</v>
       </c>
       <c r="M31" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷏</v>
       </c>
       <c r="N31" t="str">
@@ -10816,11 +11048,19 @@
         <v>䷏豫</v>
       </c>
       <c r="P31" t="str">
+        <f t="shared" si="5"/>
+        <v>䷏p</v>
+      </c>
+      <c r="Q31" t="str">
         <f t="shared" si="6"/>
-        <v>䷏</v>
-      </c>
-    </row>
-    <row r="32" spans="2:16">
+        <v>&lt;ruby&gt;䷏&lt;rt&gt;&amp;#x202E;豫&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R31" t="str">
+        <f t="shared" si="7"/>
+        <v>䷏q</v>
+      </c>
+    </row>
+    <row r="32" spans="2:18">
       <c r="B32" t="str">
         <f t="shared" si="1"/>
         <v>4DD0</v>
@@ -10836,7 +11076,7 @@
         <v>17</v>
       </c>
       <c r="F32" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷐</v>
       </c>
       <c r="G32" t="s">
@@ -10859,7 +11099,7 @@
         <v>⚋⚊⚊⚋⚋⚊</v>
       </c>
       <c r="M32" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷐</v>
       </c>
       <c r="N32" t="str">
@@ -10871,11 +11111,19 @@
         <v>䷐隨</v>
       </c>
       <c r="P32" t="str">
+        <f t="shared" si="5"/>
+        <v>䷐p</v>
+      </c>
+      <c r="Q32" t="str">
         <f t="shared" si="6"/>
-        <v>䷐</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16">
+        <v>&lt;ruby&gt;䷐&lt;rt&gt;&amp;#x202E;隨&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R32" t="str">
+        <f t="shared" si="7"/>
+        <v>䷐q</v>
+      </c>
+    </row>
+    <row r="33" spans="2:18">
       <c r="B33" t="str">
         <f t="shared" si="1"/>
         <v>4DD1</v>
@@ -10891,7 +11139,7 @@
         <v>18</v>
       </c>
       <c r="F33" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷑</v>
       </c>
       <c r="G33" t="s">
@@ -10914,7 +11162,7 @@
         <v>⚊⚋⚋⚊⚊⚋</v>
       </c>
       <c r="M33" t="str">
-        <f t="shared" si="6"/>
+        <f t="shared" si="9"/>
         <v>䷑</v>
       </c>
       <c r="N33" t="str">
@@ -10926,11 +11174,19 @@
         <v>䷑蠱</v>
       </c>
       <c r="P33" t="str">
+        <f t="shared" si="5"/>
+        <v>䷑p</v>
+      </c>
+      <c r="Q33" t="str">
         <f t="shared" si="6"/>
-        <v>䷑</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16">
+        <v>&lt;ruby&gt;䷑&lt;rt&gt;&amp;#x202E;蠱&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R33" t="str">
+        <f t="shared" si="7"/>
+        <v>䷑q</v>
+      </c>
+    </row>
+    <row r="34" spans="2:18">
       <c r="B34" t="str">
         <f t="shared" si="1"/>
         <v>4DD2</v>
@@ -10946,7 +11202,7 @@
         <v>19</v>
       </c>
       <c r="F34" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷒</v>
       </c>
       <c r="G34" t="s">
@@ -10969,7 +11225,7 @@
         <v>⚋⚋⚋⚋⚊⚊</v>
       </c>
       <c r="M34" t="str">
-        <f t="shared" ref="M34:P49" si="7">_xlfn.UNICHAR($C34)</f>
+        <f t="shared" ref="M34:M49" si="10">_xlfn.UNICHAR($C34)</f>
         <v>䷒</v>
       </c>
       <c r="N34" t="str">
@@ -10981,11 +11237,19 @@
         <v>䷒臨</v>
       </c>
       <c r="P34" t="str">
+        <f t="shared" si="5"/>
+        <v>䷒p</v>
+      </c>
+      <c r="Q34" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷒&lt;rt&gt;&amp;#x202E;臨&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R34" t="str">
         <f t="shared" si="7"/>
-        <v>䷒</v>
-      </c>
-    </row>
-    <row r="35" spans="2:16">
+        <v>䷒q</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18">
       <c r="B35" t="str">
         <f t="shared" si="1"/>
         <v>4DD3</v>
@@ -11001,7 +11265,7 @@
         <v>20</v>
       </c>
       <c r="F35" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷓</v>
       </c>
       <c r="G35" t="s">
@@ -11024,7 +11288,7 @@
         <v>⚊⚊⚋⚋⚋⚋</v>
       </c>
       <c r="M35" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷓</v>
       </c>
       <c r="N35" t="str">
@@ -11036,11 +11300,19 @@
         <v>䷓觀</v>
       </c>
       <c r="P35" t="str">
+        <f t="shared" si="5"/>
+        <v>䷓p</v>
+      </c>
+      <c r="Q35" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷓&lt;rt&gt;&amp;#x202E;觀&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R35" t="str">
         <f t="shared" si="7"/>
-        <v>䷓</v>
-      </c>
-    </row>
-    <row r="36" spans="2:16">
+        <v>䷓q</v>
+      </c>
+    </row>
+    <row r="36" spans="2:18">
       <c r="B36" t="str">
         <f t="shared" si="1"/>
         <v>4DD4</v>
@@ -11056,7 +11328,7 @@
         <v>21</v>
       </c>
       <c r="F36" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷔</v>
       </c>
       <c r="G36" t="s">
@@ -11079,7 +11351,7 @@
         <v>⚊⚋⚊⚋⚋⚊</v>
       </c>
       <c r="M36" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷔</v>
       </c>
       <c r="N36" t="str">
@@ -11091,11 +11363,19 @@
         <v>䷔噬嗑</v>
       </c>
       <c r="P36" t="str">
+        <f t="shared" si="5"/>
+        <v>䷔p</v>
+      </c>
+      <c r="Q36" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷔&lt;rt&gt;&amp;#x202E;噬嗑&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R36" t="str">
         <f t="shared" si="7"/>
-        <v>䷔</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16">
+        <v>䷔q</v>
+      </c>
+    </row>
+    <row r="37" spans="2:18">
       <c r="B37" t="str">
         <f t="shared" si="1"/>
         <v>4DD5</v>
@@ -11111,7 +11391,7 @@
         <v>22</v>
       </c>
       <c r="F37" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷕</v>
       </c>
       <c r="G37" t="s">
@@ -11134,7 +11414,7 @@
         <v>⚊⚋⚋⚊⚋⚊</v>
       </c>
       <c r="M37" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷕</v>
       </c>
       <c r="N37" t="str">
@@ -11146,11 +11426,19 @@
         <v>䷕賁</v>
       </c>
       <c r="P37" t="str">
+        <f t="shared" si="5"/>
+        <v>䷕p</v>
+      </c>
+      <c r="Q37" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷕&lt;rt&gt;&amp;#x202E;賁&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R37" t="str">
         <f t="shared" si="7"/>
-        <v>䷕</v>
-      </c>
-    </row>
-    <row r="38" spans="2:16">
+        <v>䷕q</v>
+      </c>
+    </row>
+    <row r="38" spans="2:18">
       <c r="B38" t="str">
         <f t="shared" si="1"/>
         <v>4DD6</v>
@@ -11166,7 +11454,7 @@
         <v>23</v>
       </c>
       <c r="F38" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷖</v>
       </c>
       <c r="G38" t="s">
@@ -11189,7 +11477,7 @@
         <v>⚊⚋⚋⚋⚋⚋</v>
       </c>
       <c r="M38" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷖</v>
       </c>
       <c r="N38" t="str">
@@ -11201,11 +11489,19 @@
         <v>䷖剝</v>
       </c>
       <c r="P38" t="str">
+        <f t="shared" si="5"/>
+        <v>䷖p</v>
+      </c>
+      <c r="Q38" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷖&lt;rt&gt;&amp;#x202E;剝&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R38" t="str">
         <f t="shared" si="7"/>
-        <v>䷖</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16">
+        <v>䷖q</v>
+      </c>
+    </row>
+    <row r="39" spans="2:18">
       <c r="B39" t="str">
         <f t="shared" si="1"/>
         <v>4DD7</v>
@@ -11221,7 +11517,7 @@
         <v>24</v>
       </c>
       <c r="F39" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷗</v>
       </c>
       <c r="G39" t="s">
@@ -11244,7 +11540,7 @@
         <v>⚋⚋⚋⚋⚋⚊</v>
       </c>
       <c r="M39" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷗</v>
       </c>
       <c r="N39" t="str">
@@ -11256,11 +11552,19 @@
         <v>䷗復</v>
       </c>
       <c r="P39" t="str">
+        <f t="shared" si="5"/>
+        <v>䷗p</v>
+      </c>
+      <c r="Q39" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷗&lt;rt&gt;&amp;#x202E;復&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R39" t="str">
         <f t="shared" si="7"/>
-        <v>䷗</v>
-      </c>
-    </row>
-    <row r="40" spans="2:16">
+        <v>䷗q</v>
+      </c>
+    </row>
+    <row r="40" spans="2:18">
       <c r="B40" t="str">
         <f t="shared" si="1"/>
         <v>4DD8</v>
@@ -11276,7 +11580,7 @@
         <v>25</v>
       </c>
       <c r="F40" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷘</v>
       </c>
       <c r="G40" t="s">
@@ -11299,7 +11603,7 @@
         <v>⚊⚊⚊⚋⚋⚊</v>
       </c>
       <c r="M40" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷘</v>
       </c>
       <c r="N40" t="str">
@@ -11311,11 +11615,19 @@
         <v>䷘无妄</v>
       </c>
       <c r="P40" t="str">
+        <f t="shared" si="5"/>
+        <v>䷘p</v>
+      </c>
+      <c r="Q40" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷘&lt;rt&gt;&amp;#x202E;无妄&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R40" t="str">
         <f t="shared" si="7"/>
-        <v>䷘</v>
-      </c>
-    </row>
-    <row r="41" spans="2:16">
+        <v>䷘q</v>
+      </c>
+    </row>
+    <row r="41" spans="2:18">
       <c r="B41" t="str">
         <f t="shared" si="1"/>
         <v>4DD9</v>
@@ -11331,7 +11643,7 @@
         <v>26</v>
       </c>
       <c r="F41" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷙</v>
       </c>
       <c r="G41" t="s">
@@ -11354,7 +11666,7 @@
         <v>⚊⚋⚋⚊⚊⚊</v>
       </c>
       <c r="M41" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷙</v>
       </c>
       <c r="N41" t="str">
@@ -11366,11 +11678,19 @@
         <v>䷙大畜</v>
       </c>
       <c r="P41" t="str">
+        <f t="shared" si="5"/>
+        <v>䷙p</v>
+      </c>
+      <c r="Q41" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷙&lt;rt&gt;&amp;#x202E;大畜&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R41" t="str">
         <f t="shared" si="7"/>
-        <v>䷙</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16">
+        <v>䷙q</v>
+      </c>
+    </row>
+    <row r="42" spans="2:18">
       <c r="B42" t="str">
         <f t="shared" si="1"/>
         <v>4DDA</v>
@@ -11386,7 +11706,7 @@
         <v>27</v>
       </c>
       <c r="F42" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷚</v>
       </c>
       <c r="G42" t="s">
@@ -11409,7 +11729,7 @@
         <v>⚊⚋⚋⚋⚋⚊</v>
       </c>
       <c r="M42" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷚</v>
       </c>
       <c r="N42" t="str">
@@ -11421,11 +11741,19 @@
         <v>䷚頤</v>
       </c>
       <c r="P42" t="str">
+        <f t="shared" si="5"/>
+        <v>䷚p</v>
+      </c>
+      <c r="Q42" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷚&lt;rt&gt;&amp;#x202E;頤&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R42" t="str">
         <f t="shared" si="7"/>
-        <v>䷚</v>
-      </c>
-    </row>
-    <row r="43" spans="2:16">
+        <v>䷚q</v>
+      </c>
+    </row>
+    <row r="43" spans="2:18">
       <c r="B43" t="str">
         <f t="shared" si="1"/>
         <v>4DDB</v>
@@ -11441,7 +11769,7 @@
         <v>28</v>
       </c>
       <c r="F43" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷛</v>
       </c>
       <c r="G43" t="s">
@@ -11464,7 +11792,7 @@
         <v>⚋⚊⚊⚊⚊⚋</v>
       </c>
       <c r="M43" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷛</v>
       </c>
       <c r="N43" t="str">
@@ -11476,11 +11804,19 @@
         <v>䷛大過</v>
       </c>
       <c r="P43" t="str">
+        <f t="shared" si="5"/>
+        <v>䷛p</v>
+      </c>
+      <c r="Q43" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷛&lt;rt&gt;&amp;#x202E;大過&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R43" t="str">
         <f t="shared" si="7"/>
-        <v>䷛</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16">
+        <v>䷛q</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18">
       <c r="B44" t="str">
         <f t="shared" si="1"/>
         <v>4DDC</v>
@@ -11496,7 +11832,7 @@
         <v>29</v>
       </c>
       <c r="F44" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷜</v>
       </c>
       <c r="G44" t="s">
@@ -11519,7 +11855,7 @@
         <v>⚋⚊⚋⚋⚊⚋</v>
       </c>
       <c r="M44" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷜</v>
       </c>
       <c r="N44" t="str">
@@ -11531,11 +11867,19 @@
         <v>䷜坎</v>
       </c>
       <c r="P44" t="str">
+        <f t="shared" si="5"/>
+        <v>䷜p</v>
+      </c>
+      <c r="Q44" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷜&lt;rt&gt;&amp;#x202E;坎&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R44" t="str">
         <f t="shared" si="7"/>
-        <v>䷜</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16">
+        <v>䷜q</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18">
       <c r="B45" t="str">
         <f t="shared" si="1"/>
         <v>4DDD</v>
@@ -11551,7 +11895,7 @@
         <v>30</v>
       </c>
       <c r="F45" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷝</v>
       </c>
       <c r="G45" t="s">
@@ -11574,7 +11918,7 @@
         <v>⚊⚋⚊⚊⚋⚊</v>
       </c>
       <c r="M45" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷝</v>
       </c>
       <c r="N45" t="str">
@@ -11586,11 +11930,19 @@
         <v>䷝離</v>
       </c>
       <c r="P45" t="str">
+        <f t="shared" si="5"/>
+        <v>䷝p</v>
+      </c>
+      <c r="Q45" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷝&lt;rt&gt;&amp;#x202E;離&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R45" t="str">
         <f t="shared" si="7"/>
-        <v>䷝</v>
-      </c>
-    </row>
-    <row r="46" spans="2:16">
+        <v>䷝q</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18">
       <c r="B46" t="str">
         <f t="shared" si="1"/>
         <v>4DDE</v>
@@ -11606,7 +11958,7 @@
         <v>31</v>
       </c>
       <c r="F46" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷞</v>
       </c>
       <c r="G46" t="s">
@@ -11629,7 +11981,7 @@
         <v>⚋⚊⚊⚊⚋⚋</v>
       </c>
       <c r="M46" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷞</v>
       </c>
       <c r="N46" t="str">
@@ -11641,11 +11993,19 @@
         <v>䷞咸</v>
       </c>
       <c r="P46" t="str">
+        <f t="shared" si="5"/>
+        <v>䷞p</v>
+      </c>
+      <c r="Q46" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷞&lt;rt&gt;&amp;#x202E;咸&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R46" t="str">
         <f t="shared" si="7"/>
-        <v>䷞</v>
-      </c>
-    </row>
-    <row r="47" spans="2:16">
+        <v>䷞q</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18">
       <c r="B47" t="str">
         <f t="shared" si="1"/>
         <v>4DDF</v>
@@ -11661,7 +12021,7 @@
         <v>32</v>
       </c>
       <c r="F47" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷟</v>
       </c>
       <c r="G47" t="s">
@@ -11684,7 +12044,7 @@
         <v>⚋⚋⚊⚊⚊⚋</v>
       </c>
       <c r="M47" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷟</v>
       </c>
       <c r="N47" t="str">
@@ -11696,11 +12056,19 @@
         <v>䷟恆</v>
       </c>
       <c r="P47" t="str">
+        <f t="shared" si="5"/>
+        <v>䷟p</v>
+      </c>
+      <c r="Q47" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷟&lt;rt&gt;&amp;#x202E;恆&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R47" t="str">
         <f t="shared" si="7"/>
-        <v>䷟</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16">
+        <v>䷟q</v>
+      </c>
+    </row>
+    <row r="48" spans="2:18">
       <c r="B48" t="str">
         <f t="shared" si="1"/>
         <v>4DE0</v>
@@ -11716,7 +12084,7 @@
         <v>33</v>
       </c>
       <c r="F48" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷠</v>
       </c>
       <c r="G48" t="s">
@@ -11739,7 +12107,7 @@
         <v>⚊⚊⚊⚊⚋⚋</v>
       </c>
       <c r="M48" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷠</v>
       </c>
       <c r="N48" t="str">
@@ -11751,11 +12119,19 @@
         <v>䷠遯</v>
       </c>
       <c r="P48" t="str">
+        <f t="shared" si="5"/>
+        <v>䷠p</v>
+      </c>
+      <c r="Q48" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷠&lt;rt&gt;&amp;#x202E;遯&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R48" t="str">
         <f t="shared" si="7"/>
-        <v>䷠</v>
-      </c>
-    </row>
-    <row r="49" spans="2:16">
+        <v>䷠q</v>
+      </c>
+    </row>
+    <row r="49" spans="2:18">
       <c r="B49" t="str">
         <f t="shared" si="1"/>
         <v>4DE1</v>
@@ -11771,7 +12147,7 @@
         <v>34</v>
       </c>
       <c r="F49" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷡</v>
       </c>
       <c r="G49" t="s">
@@ -11794,7 +12170,7 @@
         <v>⚋⚋⚊⚊⚊⚊</v>
       </c>
       <c r="M49" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="10"/>
         <v>䷡</v>
       </c>
       <c r="N49" t="str">
@@ -11806,11 +12182,19 @@
         <v>䷡大壯</v>
       </c>
       <c r="P49" t="str">
+        <f t="shared" si="5"/>
+        <v>䷡p</v>
+      </c>
+      <c r="Q49" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷡&lt;rt&gt;&amp;#x202E;大壯&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R49" t="str">
         <f t="shared" si="7"/>
-        <v>䷡</v>
-      </c>
-    </row>
-    <row r="50" spans="2:16">
+        <v>䷡q</v>
+      </c>
+    </row>
+    <row r="50" spans="2:18">
       <c r="B50" t="str">
         <f t="shared" si="1"/>
         <v>4DE2</v>
@@ -11826,7 +12210,7 @@
         <v>35</v>
       </c>
       <c r="F50" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷢</v>
       </c>
       <c r="G50" t="s">
@@ -11849,7 +12233,7 @@
         <v>⚊⚋⚊⚋⚋⚋</v>
       </c>
       <c r="M50" t="str">
-        <f t="shared" ref="M50:P65" si="8">_xlfn.UNICHAR($C50)</f>
+        <f t="shared" ref="M50:M65" si="11">_xlfn.UNICHAR($C50)</f>
         <v>䷢</v>
       </c>
       <c r="N50" t="str">
@@ -11861,11 +12245,19 @@
         <v>䷢晉</v>
       </c>
       <c r="P50" t="str">
-        <f t="shared" si="8"/>
-        <v>䷢</v>
-      </c>
-    </row>
-    <row r="51" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷢p</v>
+      </c>
+      <c r="Q50" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷢&lt;rt&gt;&amp;#x202E;晉&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R50" t="str">
+        <f t="shared" si="7"/>
+        <v>䷢q</v>
+      </c>
+    </row>
+    <row r="51" spans="2:18">
       <c r="B51" t="str">
         <f t="shared" si="1"/>
         <v>4DE3</v>
@@ -11881,7 +12273,7 @@
         <v>36</v>
       </c>
       <c r="F51" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷣</v>
       </c>
       <c r="G51" t="s">
@@ -11904,7 +12296,7 @@
         <v>⚋⚋⚋⚊⚋⚊</v>
       </c>
       <c r="M51" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷣</v>
       </c>
       <c r="N51" t="str">
@@ -11916,11 +12308,19 @@
         <v>䷣明夷</v>
       </c>
       <c r="P51" t="str">
-        <f t="shared" si="8"/>
-        <v>䷣</v>
-      </c>
-    </row>
-    <row r="52" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷣p</v>
+      </c>
+      <c r="Q51" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷣&lt;rt&gt;&amp;#x202E;明夷&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R51" t="str">
+        <f t="shared" si="7"/>
+        <v>䷣q</v>
+      </c>
+    </row>
+    <row r="52" spans="2:18">
       <c r="B52" t="str">
         <f t="shared" si="1"/>
         <v>4DE4</v>
@@ -11936,7 +12336,7 @@
         <v>37</v>
       </c>
       <c r="F52" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷤</v>
       </c>
       <c r="G52" t="s">
@@ -11959,7 +12359,7 @@
         <v>⚊⚊⚋⚊⚋⚊</v>
       </c>
       <c r="M52" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷤</v>
       </c>
       <c r="N52" t="str">
@@ -11971,11 +12371,19 @@
         <v>䷤家人</v>
       </c>
       <c r="P52" t="str">
-        <f t="shared" si="8"/>
-        <v>䷤</v>
-      </c>
-    </row>
-    <row r="53" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷤p</v>
+      </c>
+      <c r="Q52" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷤&lt;rt&gt;&amp;#x202E;家人&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R52" t="str">
+        <f t="shared" si="7"/>
+        <v>䷤q</v>
+      </c>
+    </row>
+    <row r="53" spans="2:18">
       <c r="B53" t="str">
         <f t="shared" si="1"/>
         <v>4DE5</v>
@@ -11991,7 +12399,7 @@
         <v>38</v>
       </c>
       <c r="F53" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷥</v>
       </c>
       <c r="G53" t="s">
@@ -12014,7 +12422,7 @@
         <v>⚊⚋⚊⚋⚊⚊</v>
       </c>
       <c r="M53" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷥</v>
       </c>
       <c r="N53" t="str">
@@ -12026,11 +12434,19 @@
         <v>䷥睽</v>
       </c>
       <c r="P53" t="str">
-        <f t="shared" si="8"/>
-        <v>䷥</v>
-      </c>
-    </row>
-    <row r="54" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷥p</v>
+      </c>
+      <c r="Q53" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷥&lt;rt&gt;&amp;#x202E;睽&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R53" t="str">
+        <f t="shared" si="7"/>
+        <v>䷥q</v>
+      </c>
+    </row>
+    <row r="54" spans="2:18">
       <c r="B54" t="str">
         <f t="shared" si="1"/>
         <v>4DE6</v>
@@ -12046,7 +12462,7 @@
         <v>39</v>
       </c>
       <c r="F54" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷦</v>
       </c>
       <c r="G54" t="s">
@@ -12069,7 +12485,7 @@
         <v>⚋⚊⚋⚊⚋⚋</v>
       </c>
       <c r="M54" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷦</v>
       </c>
       <c r="N54" t="str">
@@ -12081,11 +12497,19 @@
         <v>䷦蹇</v>
       </c>
       <c r="P54" t="str">
-        <f t="shared" si="8"/>
-        <v>䷦</v>
-      </c>
-    </row>
-    <row r="55" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷦p</v>
+      </c>
+      <c r="Q54" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷦&lt;rt&gt;&amp;#x202E;蹇&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R54" t="str">
+        <f t="shared" si="7"/>
+        <v>䷦q</v>
+      </c>
+    </row>
+    <row r="55" spans="2:18">
       <c r="B55" t="str">
         <f t="shared" si="1"/>
         <v>4DE7</v>
@@ -12101,7 +12525,7 @@
         <v>40</v>
       </c>
       <c r="F55" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷧</v>
       </c>
       <c r="G55" t="s">
@@ -12124,7 +12548,7 @@
         <v>⚋⚋⚊⚋⚊⚋</v>
       </c>
       <c r="M55" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷧</v>
       </c>
       <c r="N55" t="str">
@@ -12136,11 +12560,19 @@
         <v>䷧解</v>
       </c>
       <c r="P55" t="str">
-        <f t="shared" si="8"/>
-        <v>䷧</v>
-      </c>
-    </row>
-    <row r="56" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷧p</v>
+      </c>
+      <c r="Q55" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷧&lt;rt&gt;&amp;#x202E;解&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R55" t="str">
+        <f t="shared" si="7"/>
+        <v>䷧q</v>
+      </c>
+    </row>
+    <row r="56" spans="2:18">
       <c r="B56" t="str">
         <f t="shared" si="1"/>
         <v>4DE8</v>
@@ -12156,7 +12588,7 @@
         <v>41</v>
       </c>
       <c r="F56" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷨</v>
       </c>
       <c r="G56" t="s">
@@ -12179,7 +12611,7 @@
         <v>⚊⚋⚋⚋⚊⚊</v>
       </c>
       <c r="M56" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷨</v>
       </c>
       <c r="N56" t="str">
@@ -12191,11 +12623,19 @@
         <v>䷨損</v>
       </c>
       <c r="P56" t="str">
-        <f t="shared" si="8"/>
-        <v>䷨</v>
-      </c>
-    </row>
-    <row r="57" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷨p</v>
+      </c>
+      <c r="Q56" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷨&lt;rt&gt;&amp;#x202E;損&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R56" t="str">
+        <f t="shared" si="7"/>
+        <v>䷨q</v>
+      </c>
+    </row>
+    <row r="57" spans="2:18">
       <c r="B57" t="str">
         <f t="shared" si="1"/>
         <v>4DE9</v>
@@ -12211,7 +12651,7 @@
         <v>42</v>
       </c>
       <c r="F57" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷩</v>
       </c>
       <c r="G57" t="s">
@@ -12234,7 +12674,7 @@
         <v>⚊⚊⚋⚋⚋⚊</v>
       </c>
       <c r="M57" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷩</v>
       </c>
       <c r="N57" t="str">
@@ -12246,11 +12686,19 @@
         <v>䷩益</v>
       </c>
       <c r="P57" t="str">
-        <f t="shared" si="8"/>
-        <v>䷩</v>
-      </c>
-    </row>
-    <row r="58" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷩p</v>
+      </c>
+      <c r="Q57" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷩&lt;rt&gt;&amp;#x202E;益&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R57" t="str">
+        <f t="shared" si="7"/>
+        <v>䷩q</v>
+      </c>
+    </row>
+    <row r="58" spans="2:18">
       <c r="B58" t="str">
         <f t="shared" si="1"/>
         <v>4DEA</v>
@@ -12266,7 +12714,7 @@
         <v>43</v>
       </c>
       <c r="F58" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷪</v>
       </c>
       <c r="G58" t="s">
@@ -12289,7 +12737,7 @@
         <v>⚋⚊⚊⚊⚊⚊</v>
       </c>
       <c r="M58" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷪</v>
       </c>
       <c r="N58" t="str">
@@ -12301,11 +12749,19 @@
         <v>䷪夬</v>
       </c>
       <c r="P58" t="str">
-        <f t="shared" si="8"/>
-        <v>䷪</v>
-      </c>
-    </row>
-    <row r="59" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷪p</v>
+      </c>
+      <c r="Q58" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷪&lt;rt&gt;&amp;#x202E;夬&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R58" t="str">
+        <f t="shared" si="7"/>
+        <v>䷪q</v>
+      </c>
+    </row>
+    <row r="59" spans="2:18">
       <c r="B59" t="str">
         <f t="shared" si="1"/>
         <v>4DEB</v>
@@ -12321,7 +12777,7 @@
         <v>44</v>
       </c>
       <c r="F59" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷫</v>
       </c>
       <c r="G59" t="s">
@@ -12344,7 +12800,7 @@
         <v>⚊⚊⚊⚊⚊⚋</v>
       </c>
       <c r="M59" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷫</v>
       </c>
       <c r="N59" t="str">
@@ -12356,11 +12812,19 @@
         <v>䷫姤</v>
       </c>
       <c r="P59" t="str">
-        <f t="shared" si="8"/>
-        <v>䷫</v>
-      </c>
-    </row>
-    <row r="60" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷫p</v>
+      </c>
+      <c r="Q59" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷫&lt;rt&gt;&amp;#x202E;姤&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R59" t="str">
+        <f t="shared" si="7"/>
+        <v>䷫q</v>
+      </c>
+    </row>
+    <row r="60" spans="2:18">
       <c r="B60" t="str">
         <f t="shared" si="1"/>
         <v>4DEC</v>
@@ -12376,7 +12840,7 @@
         <v>45</v>
       </c>
       <c r="F60" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷬</v>
       </c>
       <c r="G60" t="s">
@@ -12399,7 +12863,7 @@
         <v>⚋⚊⚊⚋⚋⚋</v>
       </c>
       <c r="M60" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷬</v>
       </c>
       <c r="N60" t="str">
@@ -12411,11 +12875,19 @@
         <v>䷬萃</v>
       </c>
       <c r="P60" t="str">
-        <f t="shared" si="8"/>
-        <v>䷬</v>
-      </c>
-    </row>
-    <row r="61" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷬p</v>
+      </c>
+      <c r="Q60" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷬&lt;rt&gt;&amp;#x202E;萃&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R60" t="str">
+        <f t="shared" si="7"/>
+        <v>䷬q</v>
+      </c>
+    </row>
+    <row r="61" spans="2:18">
       <c r="B61" t="str">
         <f t="shared" si="1"/>
         <v>4DED</v>
@@ -12431,7 +12903,7 @@
         <v>46</v>
       </c>
       <c r="F61" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷭</v>
       </c>
       <c r="G61" t="s">
@@ -12454,7 +12926,7 @@
         <v>⚋⚋⚋⚊⚊⚋</v>
       </c>
       <c r="M61" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷭</v>
       </c>
       <c r="N61" t="str">
@@ -12466,11 +12938,19 @@
         <v>䷭升</v>
       </c>
       <c r="P61" t="str">
-        <f t="shared" si="8"/>
-        <v>䷭</v>
-      </c>
-    </row>
-    <row r="62" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷭p</v>
+      </c>
+      <c r="Q61" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷭&lt;rt&gt;&amp;#x202E;升&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R61" t="str">
+        <f t="shared" si="7"/>
+        <v>䷭q</v>
+      </c>
+    </row>
+    <row r="62" spans="2:18">
       <c r="B62" t="str">
         <f t="shared" si="1"/>
         <v>4DEE</v>
@@ -12486,7 +12966,7 @@
         <v>47</v>
       </c>
       <c r="F62" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷮</v>
       </c>
       <c r="G62" t="s">
@@ -12509,7 +12989,7 @@
         <v>⚋⚊⚊⚋⚊⚋</v>
       </c>
       <c r="M62" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷮</v>
       </c>
       <c r="N62" t="str">
@@ -12521,11 +13001,19 @@
         <v>䷮困</v>
       </c>
       <c r="P62" t="str">
-        <f t="shared" si="8"/>
-        <v>䷮</v>
-      </c>
-    </row>
-    <row r="63" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷮p</v>
+      </c>
+      <c r="Q62" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷮&lt;rt&gt;&amp;#x202E;困&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R62" t="str">
+        <f t="shared" si="7"/>
+        <v>䷮q</v>
+      </c>
+    </row>
+    <row r="63" spans="2:18">
       <c r="B63" t="str">
         <f t="shared" si="1"/>
         <v>4DEF</v>
@@ -12541,7 +13029,7 @@
         <v>48</v>
       </c>
       <c r="F63" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷯</v>
       </c>
       <c r="G63" t="s">
@@ -12564,7 +13052,7 @@
         <v>⚋⚊⚋⚊⚊⚋</v>
       </c>
       <c r="M63" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷯</v>
       </c>
       <c r="N63" t="str">
@@ -12576,11 +13064,19 @@
         <v>䷯井</v>
       </c>
       <c r="P63" t="str">
-        <f t="shared" si="8"/>
-        <v>䷯</v>
-      </c>
-    </row>
-    <row r="64" spans="2:16">
+        <f t="shared" si="5"/>
+        <v>䷯p</v>
+      </c>
+      <c r="Q63" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷯&lt;rt&gt;&amp;#x202E;井&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R63" t="str">
+        <f t="shared" si="7"/>
+        <v>䷯q</v>
+      </c>
+    </row>
+    <row r="64" spans="2:18">
       <c r="B64" t="str">
         <f t="shared" si="1"/>
         <v>4DF0</v>
@@ -12596,7 +13092,7 @@
         <v>49</v>
       </c>
       <c r="F64" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷰</v>
       </c>
       <c r="G64" t="s">
@@ -12619,7 +13115,7 @@
         <v>⚋⚊⚊⚊⚋⚊</v>
       </c>
       <c r="M64" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷰</v>
       </c>
       <c r="N64" t="str">
@@ -12631,11 +13127,19 @@
         <v>䷰革</v>
       </c>
       <c r="P64" t="str">
-        <f t="shared" si="8"/>
-        <v>䷰</v>
-      </c>
-    </row>
-    <row r="65" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>䷰p</v>
+      </c>
+      <c r="Q64" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷰&lt;rt&gt;&amp;#x202E;革&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R64" t="str">
+        <f t="shared" si="7"/>
+        <v>䷰q</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18">
       <c r="B65" t="str">
         <f t="shared" si="1"/>
         <v>4DF1</v>
@@ -12651,7 +13155,7 @@
         <v>50</v>
       </c>
       <c r="F65" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷱</v>
       </c>
       <c r="G65" t="s">
@@ -12674,7 +13178,7 @@
         <v>⚊⚋⚊⚊⚊⚋</v>
       </c>
       <c r="M65" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="11"/>
         <v>䷱</v>
       </c>
       <c r="N65" t="str">
@@ -12686,11 +13190,19 @@
         <v>䷱鼎</v>
       </c>
       <c r="P65" t="str">
-        <f t="shared" si="8"/>
-        <v>䷱</v>
-      </c>
-    </row>
-    <row r="66" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>䷱p</v>
+      </c>
+      <c r="Q65" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷱&lt;rt&gt;&amp;#x202E;鼎&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R65" t="str">
+        <f t="shared" si="7"/>
+        <v>䷱q</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18">
       <c r="B66" t="str">
         <f t="shared" si="1"/>
         <v>4DF2</v>
@@ -12706,7 +13218,7 @@
         <v>51</v>
       </c>
       <c r="F66" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷲</v>
       </c>
       <c r="G66" t="s">
@@ -12729,7 +13241,7 @@
         <v>⚋⚋⚊⚋⚋⚊</v>
       </c>
       <c r="M66" t="str">
-        <f t="shared" ref="M66:P81" si="9">_xlfn.UNICHAR($C66)</f>
+        <f t="shared" ref="M66:M81" si="12">_xlfn.UNICHAR($C66)</f>
         <v>䷲</v>
       </c>
       <c r="N66" t="str">
@@ -12741,13 +13253,21 @@
         <v>䷲震</v>
       </c>
       <c r="P66" t="str">
-        <f t="shared" si="9"/>
-        <v>䷲</v>
-      </c>
-    </row>
-    <row r="67" spans="1:16">
+        <f t="shared" si="5"/>
+        <v>䷲p</v>
+      </c>
+      <c r="Q66" t="str">
+        <f t="shared" si="6"/>
+        <v>&lt;ruby&gt;䷲&lt;rt&gt;&amp;#x202E;震&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R66" t="str">
+        <f t="shared" si="7"/>
+        <v>䷲q</v>
+      </c>
+    </row>
+    <row r="67" spans="1:18">
       <c r="B67" t="str">
-        <f t="shared" ref="B67:B130" si="10">DEC2HEX($C67)</f>
+        <f t="shared" ref="B67:B130" si="13">DEC2HEX($C67)</f>
         <v>4DF3</v>
       </c>
       <c r="C67" cm="1">
@@ -12761,7 +13281,7 @@
         <v>52</v>
       </c>
       <c r="F67" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷳</v>
       </c>
       <c r="G67" t="s">
@@ -12780,29 +13300,37 @@
         <v>788788</v>
       </c>
       <c r="L67" t="str">
-        <f t="shared" ref="L67:L85" si="11">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J67,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
+        <f t="shared" ref="L67:L85" si="14">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J67,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
         <v>⚊⚋⚋⚊⚋⚋</v>
       </c>
       <c r="M67" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷳</v>
       </c>
       <c r="N67" t="str">
-        <f t="shared" ref="N67:N130" si="12">IF($H67="",$G67,$H67)</f>
+        <f t="shared" ref="N67:N130" si="15">IF($H67="",$G67,$H67)</f>
         <v>艮</v>
       </c>
       <c r="O67" t="str">
-        <f t="shared" ref="O67:O130" si="13">M67&amp;N67</f>
+        <f t="shared" ref="O67:O130" si="16">M67&amp;N67</f>
         <v>䷳艮</v>
       </c>
       <c r="P67" t="str">
-        <f t="shared" si="9"/>
-        <v>䷳</v>
-      </c>
-    </row>
-    <row r="68" spans="1:16">
+        <f t="shared" ref="P67:P130" si="17">_xlfn.UNICHAR($C67)&amp;"p"</f>
+        <v>䷳p</v>
+      </c>
+      <c r="Q67" t="str">
+        <f t="shared" ref="Q67:Q130" si="18">"&lt;ruby&gt;"&amp;$M67&amp;"&lt;rt&gt;&amp;#x202E;"&amp;$N67&amp;"&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;"</f>
+        <v>&lt;ruby&gt;䷳&lt;rt&gt;&amp;#x202E;艮&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R67" t="str">
+        <f t="shared" ref="R67:R130" si="19">_xlfn.UNICHAR($C67)&amp;"q"</f>
+        <v>䷳q</v>
+      </c>
+    </row>
+    <row r="68" spans="1:18">
       <c r="B68" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>4DF4</v>
       </c>
       <c r="C68" cm="1">
@@ -12816,7 +13344,7 @@
         <v>53</v>
       </c>
       <c r="F68" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷴</v>
       </c>
       <c r="G68" t="s">
@@ -12835,29 +13363,37 @@
         <v>778788</v>
       </c>
       <c r="L68" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚊⚊⚋⚊⚋⚋</v>
       </c>
       <c r="M68" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷴</v>
       </c>
       <c r="N68" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>漸</v>
       </c>
       <c r="O68" t="str">
+        <f t="shared" si="16"/>
+        <v>䷴漸</v>
+      </c>
+      <c r="P68" t="str">
+        <f t="shared" si="17"/>
+        <v>䷴p</v>
+      </c>
+      <c r="Q68" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷴&lt;rt&gt;&amp;#x202E;漸&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R68" t="str">
+        <f t="shared" si="19"/>
+        <v>䷴q</v>
+      </c>
+    </row>
+    <row r="69" spans="1:18">
+      <c r="B69" t="str">
         <f t="shared" si="13"/>
-        <v>䷴漸</v>
-      </c>
-      <c r="P68" t="str">
-        <f t="shared" si="9"/>
-        <v>䷴</v>
-      </c>
-    </row>
-    <row r="69" spans="1:16">
-      <c r="B69" t="str">
-        <f t="shared" si="10"/>
         <v>4DF5</v>
       </c>
       <c r="C69" cm="1">
@@ -12871,7 +13407,7 @@
         <v>54</v>
       </c>
       <c r="F69" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷵</v>
       </c>
       <c r="G69" t="s">
@@ -12890,29 +13426,37 @@
         <v>887877</v>
       </c>
       <c r="L69" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚋⚋⚊⚋⚊⚊</v>
       </c>
       <c r="M69" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷵</v>
       </c>
       <c r="N69" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>歸妹</v>
       </c>
       <c r="O69" t="str">
+        <f t="shared" si="16"/>
+        <v>䷵歸妹</v>
+      </c>
+      <c r="P69" t="str">
+        <f t="shared" si="17"/>
+        <v>䷵p</v>
+      </c>
+      <c r="Q69" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷵&lt;rt&gt;&amp;#x202E;歸妹&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R69" t="str">
+        <f t="shared" si="19"/>
+        <v>䷵q</v>
+      </c>
+    </row>
+    <row r="70" spans="1:18">
+      <c r="B70" t="str">
         <f t="shared" si="13"/>
-        <v>䷵歸妹</v>
-      </c>
-      <c r="P69" t="str">
-        <f t="shared" si="9"/>
-        <v>䷵</v>
-      </c>
-    </row>
-    <row r="70" spans="1:16">
-      <c r="B70" t="str">
-        <f t="shared" si="10"/>
         <v>4DF6</v>
       </c>
       <c r="C70" cm="1">
@@ -12926,7 +13470,7 @@
         <v>55</v>
       </c>
       <c r="F70" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷶</v>
       </c>
       <c r="G70" t="s">
@@ -12945,29 +13489,37 @@
         <v>887787</v>
       </c>
       <c r="L70" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚋⚋⚊⚊⚋⚊</v>
       </c>
       <c r="M70" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷶</v>
       </c>
       <c r="N70" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>豐</v>
       </c>
       <c r="O70" t="str">
+        <f t="shared" si="16"/>
+        <v>䷶豐</v>
+      </c>
+      <c r="P70" t="str">
+        <f t="shared" si="17"/>
+        <v>䷶p</v>
+      </c>
+      <c r="Q70" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷶&lt;rt&gt;&amp;#x202E;豐&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R70" t="str">
+        <f t="shared" si="19"/>
+        <v>䷶q</v>
+      </c>
+    </row>
+    <row r="71" spans="1:18">
+      <c r="B71" t="str">
         <f t="shared" si="13"/>
-        <v>䷶豐</v>
-      </c>
-      <c r="P70" t="str">
-        <f t="shared" si="9"/>
-        <v>䷶</v>
-      </c>
-    </row>
-    <row r="71" spans="1:16">
-      <c r="B71" t="str">
-        <f t="shared" si="10"/>
         <v>4DF7</v>
       </c>
       <c r="C71" cm="1">
@@ -12981,7 +13533,7 @@
         <v>56</v>
       </c>
       <c r="F71" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷷</v>
       </c>
       <c r="G71" t="s">
@@ -13000,29 +13552,37 @@
         <v>787788</v>
       </c>
       <c r="L71" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚊⚋⚊⚊⚋⚋</v>
       </c>
       <c r="M71" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷷</v>
       </c>
       <c r="N71" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>旅</v>
       </c>
       <c r="O71" t="str">
+        <f t="shared" si="16"/>
+        <v>䷷旅</v>
+      </c>
+      <c r="P71" t="str">
+        <f t="shared" si="17"/>
+        <v>䷷p</v>
+      </c>
+      <c r="Q71" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷷&lt;rt&gt;&amp;#x202E;旅&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R71" t="str">
+        <f t="shared" si="19"/>
+        <v>䷷q</v>
+      </c>
+    </row>
+    <row r="72" spans="1:18">
+      <c r="B72" t="str">
         <f t="shared" si="13"/>
-        <v>䷷旅</v>
-      </c>
-      <c r="P71" t="str">
-        <f t="shared" si="9"/>
-        <v>䷷</v>
-      </c>
-    </row>
-    <row r="72" spans="1:16">
-      <c r="B72" t="str">
-        <f t="shared" si="10"/>
         <v>4DF8</v>
       </c>
       <c r="C72" cm="1">
@@ -13036,7 +13596,7 @@
         <v>57</v>
       </c>
       <c r="F72" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷸</v>
       </c>
       <c r="G72" t="s">
@@ -13055,29 +13615,37 @@
         <v>778778</v>
       </c>
       <c r="L72" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚊⚊⚋⚊⚊⚋</v>
       </c>
       <c r="M72" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷸</v>
       </c>
       <c r="N72" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>巽</v>
       </c>
       <c r="O72" t="str">
+        <f t="shared" si="16"/>
+        <v>䷸巽</v>
+      </c>
+      <c r="P72" t="str">
+        <f t="shared" si="17"/>
+        <v>䷸p</v>
+      </c>
+      <c r="Q72" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷸&lt;rt&gt;&amp;#x202E;巽&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R72" t="str">
+        <f t="shared" si="19"/>
+        <v>䷸q</v>
+      </c>
+    </row>
+    <row r="73" spans="1:18">
+      <c r="B73" t="str">
         <f t="shared" si="13"/>
-        <v>䷸巽</v>
-      </c>
-      <c r="P72" t="str">
-        <f t="shared" si="9"/>
-        <v>䷸</v>
-      </c>
-    </row>
-    <row r="73" spans="1:16">
-      <c r="B73" t="str">
-        <f t="shared" si="10"/>
         <v>4DF9</v>
       </c>
       <c r="C73" cm="1">
@@ -13091,7 +13659,7 @@
         <v>58</v>
       </c>
       <c r="F73" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷹</v>
       </c>
       <c r="G73" t="s">
@@ -13110,29 +13678,37 @@
         <v>877877</v>
       </c>
       <c r="L73" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚋⚊⚊⚋⚊⚊</v>
       </c>
       <c r="M73" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷹</v>
       </c>
       <c r="N73" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>兌</v>
       </c>
       <c r="O73" t="str">
+        <f t="shared" si="16"/>
+        <v>䷹兌</v>
+      </c>
+      <c r="P73" t="str">
+        <f t="shared" si="17"/>
+        <v>䷹p</v>
+      </c>
+      <c r="Q73" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷹&lt;rt&gt;&amp;#x202E;兌&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R73" t="str">
+        <f t="shared" si="19"/>
+        <v>䷹q</v>
+      </c>
+    </row>
+    <row r="74" spans="1:18">
+      <c r="B74" t="str">
         <f t="shared" si="13"/>
-        <v>䷹兌</v>
-      </c>
-      <c r="P73" t="str">
-        <f t="shared" si="9"/>
-        <v>䷹</v>
-      </c>
-    </row>
-    <row r="74" spans="1:16">
-      <c r="B74" t="str">
-        <f t="shared" si="10"/>
         <v>4DFA</v>
       </c>
       <c r="C74" cm="1">
@@ -13146,7 +13722,7 @@
         <v>59</v>
       </c>
       <c r="F74" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷺</v>
       </c>
       <c r="G74" t="s">
@@ -13165,29 +13741,37 @@
         <v>778878</v>
       </c>
       <c r="L74" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚊⚊⚋⚋⚊⚋</v>
       </c>
       <c r="M74" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷺</v>
       </c>
       <c r="N74" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>渙</v>
       </c>
       <c r="O74" t="str">
+        <f t="shared" si="16"/>
+        <v>䷺渙</v>
+      </c>
+      <c r="P74" t="str">
+        <f t="shared" si="17"/>
+        <v>䷺p</v>
+      </c>
+      <c r="Q74" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷺&lt;rt&gt;&amp;#x202E;渙&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R74" t="str">
+        <f t="shared" si="19"/>
+        <v>䷺q</v>
+      </c>
+    </row>
+    <row r="75" spans="1:18">
+      <c r="B75" t="str">
         <f t="shared" si="13"/>
-        <v>䷺渙</v>
-      </c>
-      <c r="P74" t="str">
-        <f t="shared" si="9"/>
-        <v>䷺</v>
-      </c>
-    </row>
-    <row r="75" spans="1:16">
-      <c r="B75" t="str">
-        <f t="shared" si="10"/>
         <v>4DFB</v>
       </c>
       <c r="C75" cm="1">
@@ -13201,7 +13785,7 @@
         <v>60</v>
       </c>
       <c r="F75" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷻</v>
       </c>
       <c r="G75" t="s">
@@ -13220,29 +13804,37 @@
         <v>878877</v>
       </c>
       <c r="L75" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚋⚊⚋⚋⚊⚊</v>
       </c>
       <c r="M75" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷻</v>
       </c>
       <c r="N75" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>節</v>
       </c>
       <c r="O75" t="str">
+        <f t="shared" si="16"/>
+        <v>䷻節</v>
+      </c>
+      <c r="P75" t="str">
+        <f t="shared" si="17"/>
+        <v>䷻p</v>
+      </c>
+      <c r="Q75" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷻&lt;rt&gt;&amp;#x202E;節&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R75" t="str">
+        <f t="shared" si="19"/>
+        <v>䷻q</v>
+      </c>
+    </row>
+    <row r="76" spans="1:18">
+      <c r="B76" t="str">
         <f t="shared" si="13"/>
-        <v>䷻節</v>
-      </c>
-      <c r="P75" t="str">
-        <f t="shared" si="9"/>
-        <v>䷻</v>
-      </c>
-    </row>
-    <row r="76" spans="1:16">
-      <c r="B76" t="str">
-        <f t="shared" si="10"/>
         <v>4DFC</v>
       </c>
       <c r="C76" cm="1">
@@ -13256,7 +13848,7 @@
         <v>61</v>
       </c>
       <c r="F76" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷼</v>
       </c>
       <c r="G76" t="s">
@@ -13275,29 +13867,37 @@
         <v>778877</v>
       </c>
       <c r="L76" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚊⚊⚋⚋⚊⚊</v>
       </c>
       <c r="M76" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷼</v>
       </c>
       <c r="N76" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>中孚</v>
       </c>
       <c r="O76" t="str">
+        <f t="shared" si="16"/>
+        <v>䷼中孚</v>
+      </c>
+      <c r="P76" t="str">
+        <f t="shared" si="17"/>
+        <v>䷼p</v>
+      </c>
+      <c r="Q76" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷼&lt;rt&gt;&amp;#x202E;中孚&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R76" t="str">
+        <f t="shared" si="19"/>
+        <v>䷼q</v>
+      </c>
+    </row>
+    <row r="77" spans="1:18">
+      <c r="B77" t="str">
         <f t="shared" si="13"/>
-        <v>䷼中孚</v>
-      </c>
-      <c r="P76" t="str">
-        <f t="shared" si="9"/>
-        <v>䷼</v>
-      </c>
-    </row>
-    <row r="77" spans="1:16">
-      <c r="B77" t="str">
-        <f t="shared" si="10"/>
         <v>4DFD</v>
       </c>
       <c r="C77" cm="1">
@@ -13311,7 +13911,7 @@
         <v>62</v>
       </c>
       <c r="F77" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷽</v>
       </c>
       <c r="G77" t="s">
@@ -13330,29 +13930,37 @@
         <v>887788</v>
       </c>
       <c r="L77" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚋⚋⚊⚊⚋⚋</v>
       </c>
       <c r="M77" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷽</v>
       </c>
       <c r="N77" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>小過</v>
       </c>
       <c r="O77" t="str">
+        <f t="shared" si="16"/>
+        <v>䷽小過</v>
+      </c>
+      <c r="P77" t="str">
+        <f t="shared" si="17"/>
+        <v>䷽p</v>
+      </c>
+      <c r="Q77" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷽&lt;rt&gt;&amp;#x202E;小過&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R77" t="str">
+        <f t="shared" si="19"/>
+        <v>䷽q</v>
+      </c>
+    </row>
+    <row r="78" spans="1:18">
+      <c r="B78" t="str">
         <f t="shared" si="13"/>
-        <v>䷽小過</v>
-      </c>
-      <c r="P77" t="str">
-        <f t="shared" si="9"/>
-        <v>䷽</v>
-      </c>
-    </row>
-    <row r="78" spans="1:16">
-      <c r="B78" t="str">
-        <f t="shared" si="10"/>
         <v>4DFE</v>
       </c>
       <c r="C78" cm="1">
@@ -13366,7 +13974,7 @@
         <v>63</v>
       </c>
       <c r="F78" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷾</v>
       </c>
       <c r="G78" t="s">
@@ -13385,29 +13993,37 @@
         <v>878787</v>
       </c>
       <c r="L78" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚋⚊⚋⚊⚋⚊</v>
       </c>
       <c r="M78" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷾</v>
       </c>
       <c r="N78" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>旣濟</v>
       </c>
       <c r="O78" t="str">
+        <f t="shared" si="16"/>
+        <v>䷾旣濟</v>
+      </c>
+      <c r="P78" t="str">
+        <f t="shared" si="17"/>
+        <v>䷾p</v>
+      </c>
+      <c r="Q78" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷾&lt;rt&gt;&amp;#x202E;旣濟&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R78" t="str">
+        <f t="shared" si="19"/>
+        <v>䷾q</v>
+      </c>
+    </row>
+    <row r="79" spans="1:18">
+      <c r="B79" t="str">
         <f t="shared" si="13"/>
-        <v>䷾旣濟</v>
-      </c>
-      <c r="P78" t="str">
-        <f t="shared" si="9"/>
-        <v>䷾</v>
-      </c>
-    </row>
-    <row r="79" spans="1:16">
-      <c r="B79" t="str">
-        <f t="shared" si="10"/>
         <v>4DFF</v>
       </c>
       <c r="C79" cm="1">
@@ -13421,7 +14037,7 @@
         <v>64</v>
       </c>
       <c r="F79" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>䷿</v>
       </c>
       <c r="G79" t="s">
@@ -13440,32 +14056,40 @@
         <v>787878</v>
       </c>
       <c r="L79" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚊⚋⚊⚋⚊⚋</v>
       </c>
       <c r="M79" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>䷿</v>
       </c>
       <c r="N79" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>未濟</v>
       </c>
       <c r="O79" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>䷿未濟</v>
       </c>
       <c r="P79" t="str">
-        <f t="shared" si="9"/>
-        <v>䷿</v>
-      </c>
-    </row>
-    <row r="80" spans="1:16">
+        <f t="shared" si="17"/>
+        <v>䷿p</v>
+      </c>
+      <c r="Q79" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;䷿&lt;rt&gt;&amp;#x202E;未濟&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R79" t="str">
+        <f t="shared" si="19"/>
+        <v>䷿q</v>
+      </c>
+    </row>
+    <row r="80" spans="1:18">
       <c r="A80" t="s">
         <v>1</v>
       </c>
       <c r="B80" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D300</v>
       </c>
       <c r="C80" cm="1">
@@ -13479,7 +14103,7 @@
         <v>3</v>
       </c>
       <c r="F80" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌀</v>
       </c>
       <c r="H80" t="s">
@@ -13498,29 +14122,37 @@
         <v>9</v>
       </c>
       <c r="L80" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>𝌀</v>
       </c>
       <c r="M80" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>𝌀</v>
       </c>
       <c r="N80" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>人</v>
       </c>
       <c r="O80" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌀人</v>
+      </c>
+      <c r="P80" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌀p</v>
+      </c>
+      <c r="Q80" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌀&lt;rt&gt;&amp;#x202E;人&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R80" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌀q</v>
+      </c>
+    </row>
+    <row r="81" spans="2:18">
+      <c r="B81" t="str">
         <f t="shared" si="13"/>
-        <v>𝌀人</v>
-      </c>
-      <c r="P80" t="str">
-        <f t="shared" si="9"/>
-        <v>𝌀</v>
-      </c>
-    </row>
-    <row r="81" spans="2:16">
-      <c r="B81" t="str">
-        <f t="shared" si="10"/>
         <v>1D301</v>
       </c>
       <c r="C81" cm="1">
@@ -13534,7 +14166,7 @@
         <v>5</v>
       </c>
       <c r="F81" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌁</v>
       </c>
       <c r="H81" t="s">
@@ -13556,29 +14188,37 @@
         <v>79</v>
       </c>
       <c r="L81" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚊𝌀</v>
       </c>
       <c r="M81" t="str">
-        <f t="shared" si="9"/>
+        <f t="shared" si="12"/>
         <v>𝌁</v>
       </c>
       <c r="N81" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>天人</v>
       </c>
       <c r="O81" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌁天人</v>
+      </c>
+      <c r="P81" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌁p</v>
+      </c>
+      <c r="Q81" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌁&lt;rt&gt;&amp;#x202E;天人&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R81" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌁q</v>
+      </c>
+    </row>
+    <row r="82" spans="2:18">
+      <c r="B82" t="str">
         <f t="shared" si="13"/>
-        <v>𝌁天人</v>
-      </c>
-      <c r="P81" t="str">
-        <f t="shared" si="9"/>
-        <v>𝌁</v>
-      </c>
-    </row>
-    <row r="82" spans="2:16">
-      <c r="B82" t="str">
-        <f t="shared" si="10"/>
         <v>1D302</v>
       </c>
       <c r="C82" cm="1">
@@ -13592,7 +14232,7 @@
         <v>6</v>
       </c>
       <c r="F82" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌂</v>
       </c>
       <c r="H82" t="s">
@@ -13614,29 +14254,37 @@
         <v>89</v>
       </c>
       <c r="L82" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>⚋𝌀</v>
       </c>
       <c r="M82" t="str">
-        <f t="shared" ref="M82:P97" si="14">_xlfn.UNICHAR($C82)</f>
+        <f t="shared" ref="M82:M97" si="20">_xlfn.UNICHAR($C82)</f>
         <v>𝌂</v>
       </c>
       <c r="N82" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>地人</v>
       </c>
       <c r="O82" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌂地人</v>
+      </c>
+      <c r="P82" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌂p</v>
+      </c>
+      <c r="Q82" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌂&lt;rt&gt;&amp;#x202E;地人&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R82" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌂q</v>
+      </c>
+    </row>
+    <row r="83" spans="2:18">
+      <c r="B83" t="str">
         <f t="shared" si="13"/>
-        <v>𝌂地人</v>
-      </c>
-      <c r="P82" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌂</v>
-      </c>
-    </row>
-    <row r="83" spans="2:16">
-      <c r="B83" t="str">
-        <f t="shared" si="10"/>
         <v>1D303</v>
       </c>
       <c r="C83" cm="1">
@@ -13650,7 +14298,7 @@
         <v>7</v>
       </c>
       <c r="F83" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌃</v>
       </c>
       <c r="H83" t="s">
@@ -13672,29 +14320,37 @@
         <v>97</v>
       </c>
       <c r="L83" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>𝌀⚊</v>
       </c>
       <c r="M83" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>𝌃</v>
       </c>
       <c r="N83" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>人天</v>
       </c>
       <c r="O83" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌃人天</v>
+      </c>
+      <c r="P83" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌃p</v>
+      </c>
+      <c r="Q83" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌃&lt;rt&gt;&amp;#x202E;人天&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R83" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌃q</v>
+      </c>
+    </row>
+    <row r="84" spans="2:18">
+      <c r="B84" t="str">
         <f t="shared" si="13"/>
-        <v>𝌃人天</v>
-      </c>
-      <c r="P83" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌃</v>
-      </c>
-    </row>
-    <row r="84" spans="2:16">
-      <c r="B84" t="str">
-        <f t="shared" si="10"/>
         <v>1D304</v>
       </c>
       <c r="C84" cm="1">
@@ -13708,7 +14364,7 @@
         <v>8</v>
       </c>
       <c r="F84" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌄</v>
       </c>
       <c r="H84" t="s">
@@ -13727,29 +14383,37 @@
         <v>98</v>
       </c>
       <c r="L84" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>𝌀⚋</v>
       </c>
       <c r="M84" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>𝌄</v>
       </c>
       <c r="N84" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>人地</v>
       </c>
       <c r="O84" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌄人地</v>
+      </c>
+      <c r="P84" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌄p</v>
+      </c>
+      <c r="Q84" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌄&lt;rt&gt;&amp;#x202E;人地&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R84" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌄q</v>
+      </c>
+    </row>
+    <row r="85" spans="2:18">
+      <c r="B85" t="str">
         <f t="shared" si="13"/>
-        <v>𝌄人地</v>
-      </c>
-      <c r="P84" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌄</v>
-      </c>
-    </row>
-    <row r="85" spans="2:16">
-      <c r="B85" t="str">
-        <f t="shared" si="10"/>
         <v>1D305</v>
       </c>
       <c r="C85" cm="1">
@@ -13763,7 +14427,7 @@
         <v>9</v>
       </c>
       <c r="F85" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌅</v>
       </c>
       <c r="H85" t="s">
@@ -13782,29 +14446,37 @@
         <v>99</v>
       </c>
       <c r="L85" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="14"/>
         <v>𝌀𝌀</v>
       </c>
       <c r="M85" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>𝌅</v>
       </c>
       <c r="N85" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>人人</v>
       </c>
       <c r="O85" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌅人人</v>
+      </c>
+      <c r="P85" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌅p</v>
+      </c>
+      <c r="Q85" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌅&lt;rt&gt;&amp;#x202E;人人&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R85" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌅q</v>
+      </c>
+    </row>
+    <row r="86" spans="2:18">
+      <c r="B86" t="str">
         <f t="shared" si="13"/>
-        <v>𝌅人人</v>
-      </c>
-      <c r="P85" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌅</v>
-      </c>
-    </row>
-    <row r="86" spans="2:16">
-      <c r="B86" t="str">
-        <f t="shared" si="10"/>
         <v>1D306</v>
       </c>
       <c r="C86" cm="1">
@@ -13818,7 +14490,7 @@
         <v>1</v>
       </c>
       <c r="F86" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌆</v>
       </c>
       <c r="H86" t="s">
@@ -13850,25 +14522,33 @@
         <v>⚊⚊⚊⚊</v>
       </c>
       <c r="M86" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>𝌆</v>
       </c>
       <c r="N86" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>中</v>
       </c>
       <c r="O86" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌆中</v>
+      </c>
+      <c r="P86" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌆p</v>
+      </c>
+      <c r="Q86" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌆&lt;rt&gt;&amp;#x202E;中&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R86" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌆q</v>
+      </c>
+    </row>
+    <row r="87" spans="2:18">
+      <c r="B87" t="str">
         <f t="shared" si="13"/>
-        <v>𝌆中</v>
-      </c>
-      <c r="P86" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌆</v>
-      </c>
-    </row>
-    <row r="87" spans="2:16">
-      <c r="B87" t="str">
-        <f t="shared" si="10"/>
         <v>1D307</v>
       </c>
       <c r="C87" cm="1">
@@ -13882,7 +14562,7 @@
         <v>2</v>
       </c>
       <c r="F87" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌇</v>
       </c>
       <c r="H87" t="s">
@@ -13910,29 +14590,37 @@
         <v>7778</v>
       </c>
       <c r="L87" t="str">
-        <f t="shared" ref="L87:L150" si="15">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J87,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
+        <f t="shared" ref="L87:L150" si="21">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J87,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
         <v>⚊⚊⚊⚋</v>
       </c>
       <c r="M87" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="20"/>
         <v>𝌇</v>
       </c>
       <c r="N87" t="str">
-        <f t="shared" si="12"/>
+        <f t="shared" si="15"/>
         <v>周</v>
       </c>
       <c r="O87" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌇周</v>
+      </c>
+      <c r="P87" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌇p</v>
+      </c>
+      <c r="Q87" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌇&lt;rt&gt;&amp;#x202E;周&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R87" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌇q</v>
+      </c>
+    </row>
+    <row r="88" spans="2:18">
+      <c r="B88" t="str">
         <f t="shared" si="13"/>
-        <v>𝌇周</v>
-      </c>
-      <c r="P87" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌇</v>
-      </c>
-    </row>
-    <row r="88" spans="2:16">
-      <c r="B88" t="str">
-        <f t="shared" si="10"/>
         <v>1D308</v>
       </c>
       <c r="C88" cm="1">
@@ -13946,7 +14634,7 @@
         <v>3</v>
       </c>
       <c r="F88" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌈</v>
       </c>
       <c r="H88" t="s">
@@ -13974,29 +14662,37 @@
         <v>7779</v>
       </c>
       <c r="L88" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚊⚊𝌀</v>
+      </c>
+      <c r="M88" t="str">
+        <f t="shared" si="20"/>
+        <v>𝌈</v>
+      </c>
+      <c r="N88" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚊⚊𝌀</v>
-      </c>
-      <c r="M88" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌈</v>
-      </c>
-      <c r="N88" t="str">
-        <f t="shared" si="12"/>
         <v>礥</v>
       </c>
       <c r="O88" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌈礥</v>
+      </c>
+      <c r="P88" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌈p</v>
+      </c>
+      <c r="Q88" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌈&lt;rt&gt;&amp;#x202E;礥&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R88" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌈q</v>
+      </c>
+    </row>
+    <row r="89" spans="2:18">
+      <c r="B89" t="str">
         <f t="shared" si="13"/>
-        <v>𝌈礥</v>
-      </c>
-      <c r="P88" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌈</v>
-      </c>
-    </row>
-    <row r="89" spans="2:16">
-      <c r="B89" t="str">
-        <f t="shared" si="10"/>
         <v>1D309</v>
       </c>
       <c r="C89" cm="1">
@@ -14010,7 +14706,7 @@
         <v>4</v>
       </c>
       <c r="F89" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌉</v>
       </c>
       <c r="H89" t="s">
@@ -14038,29 +14734,37 @@
         <v>7787</v>
       </c>
       <c r="L89" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚊⚋⚊</v>
+      </c>
+      <c r="M89" t="str">
+        <f t="shared" si="20"/>
+        <v>𝌉</v>
+      </c>
+      <c r="N89" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚊⚋⚊</v>
-      </c>
-      <c r="M89" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌉</v>
-      </c>
-      <c r="N89" t="str">
-        <f t="shared" si="12"/>
         <v>閑</v>
       </c>
       <c r="O89" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌉閑</v>
+      </c>
+      <c r="P89" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌉p</v>
+      </c>
+      <c r="Q89" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌉&lt;rt&gt;&amp;#x202E;閑&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R89" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌉q</v>
+      </c>
+    </row>
+    <row r="90" spans="2:18">
+      <c r="B90" t="str">
         <f t="shared" si="13"/>
-        <v>𝌉閑</v>
-      </c>
-      <c r="P89" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌉</v>
-      </c>
-    </row>
-    <row r="90" spans="2:16">
-      <c r="B90" t="str">
-        <f t="shared" si="10"/>
         <v>1D30A</v>
       </c>
       <c r="C90" cm="1">
@@ -14074,7 +14778,7 @@
         <v>5</v>
       </c>
       <c r="F90" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌊</v>
       </c>
       <c r="H90" t="s">
@@ -14102,29 +14806,37 @@
         <v>7788</v>
       </c>
       <c r="L90" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚊⚋⚋</v>
+      </c>
+      <c r="M90" t="str">
+        <f t="shared" si="20"/>
+        <v>𝌊</v>
+      </c>
+      <c r="N90" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚊⚋⚋</v>
-      </c>
-      <c r="M90" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌊</v>
-      </c>
-      <c r="N90" t="str">
-        <f t="shared" si="12"/>
         <v>少</v>
       </c>
       <c r="O90" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌊少</v>
+      </c>
+      <c r="P90" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌊p</v>
+      </c>
+      <c r="Q90" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌊&lt;rt&gt;&amp;#x202E;少&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R90" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌊q</v>
+      </c>
+    </row>
+    <row r="91" spans="2:18">
+      <c r="B91" t="str">
         <f t="shared" si="13"/>
-        <v>𝌊少</v>
-      </c>
-      <c r="P90" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌊</v>
-      </c>
-    </row>
-    <row r="91" spans="2:16">
-      <c r="B91" t="str">
-        <f t="shared" si="10"/>
         <v>1D30B</v>
       </c>
       <c r="C91" cm="1">
@@ -14138,7 +14850,7 @@
         <v>6</v>
       </c>
       <c r="F91" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌋</v>
       </c>
       <c r="H91" t="s">
@@ -14166,29 +14878,37 @@
         <v>7789</v>
       </c>
       <c r="L91" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚊⚋𝌀</v>
+      </c>
+      <c r="M91" t="str">
+        <f t="shared" si="20"/>
+        <v>𝌋</v>
+      </c>
+      <c r="N91" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚊⚋𝌀</v>
-      </c>
-      <c r="M91" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌋</v>
-      </c>
-      <c r="N91" t="str">
-        <f t="shared" si="12"/>
         <v>戾</v>
       </c>
       <c r="O91" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌋戾</v>
+      </c>
+      <c r="P91" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌋p</v>
+      </c>
+      <c r="Q91" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌋&lt;rt&gt;&amp;#x202E;戾&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R91" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌋q</v>
+      </c>
+    </row>
+    <row r="92" spans="2:18">
+      <c r="B92" t="str">
         <f t="shared" si="13"/>
-        <v>𝌋戾</v>
-      </c>
-      <c r="P91" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌋</v>
-      </c>
-    </row>
-    <row r="92" spans="2:16">
-      <c r="B92" t="str">
-        <f t="shared" si="10"/>
         <v>1D30C</v>
       </c>
       <c r="C92" cm="1">
@@ -14202,7 +14922,7 @@
         <v>7</v>
       </c>
       <c r="F92" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌌</v>
       </c>
       <c r="H92" t="s">
@@ -14230,29 +14950,37 @@
         <v>7797</v>
       </c>
       <c r="L92" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚊𝌀⚊</v>
+      </c>
+      <c r="M92" t="str">
+        <f t="shared" si="20"/>
+        <v>𝌌</v>
+      </c>
+      <c r="N92" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚊𝌀⚊</v>
-      </c>
-      <c r="M92" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌌</v>
-      </c>
-      <c r="N92" t="str">
-        <f t="shared" si="12"/>
         <v>上</v>
       </c>
       <c r="O92" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌌上</v>
+      </c>
+      <c r="P92" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌌p</v>
+      </c>
+      <c r="Q92" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌌&lt;rt&gt;&amp;#x202E;上&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R92" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌌q</v>
+      </c>
+    </row>
+    <row r="93" spans="2:18">
+      <c r="B93" t="str">
         <f t="shared" si="13"/>
-        <v>𝌌上</v>
-      </c>
-      <c r="P92" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌌</v>
-      </c>
-    </row>
-    <row r="93" spans="2:16">
-      <c r="B93" t="str">
-        <f t="shared" si="10"/>
         <v>1D30D</v>
       </c>
       <c r="C93" cm="1">
@@ -14266,7 +14994,7 @@
         <v>8</v>
       </c>
       <c r="F93" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌍</v>
       </c>
       <c r="H93" t="s">
@@ -14294,29 +15022,37 @@
         <v>7798</v>
       </c>
       <c r="L93" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚊𝌀⚋</v>
+      </c>
+      <c r="M93" t="str">
+        <f t="shared" si="20"/>
+        <v>𝌍</v>
+      </c>
+      <c r="N93" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚊𝌀⚋</v>
-      </c>
-      <c r="M93" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌍</v>
-      </c>
-      <c r="N93" t="str">
-        <f t="shared" si="12"/>
         <v>干</v>
       </c>
       <c r="O93" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌍干</v>
+      </c>
+      <c r="P93" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌍p</v>
+      </c>
+      <c r="Q93" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌍&lt;rt&gt;&amp;#x202E;干&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R93" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌍q</v>
+      </c>
+    </row>
+    <row r="94" spans="2:18">
+      <c r="B94" t="str">
         <f t="shared" si="13"/>
-        <v>𝌍干</v>
-      </c>
-      <c r="P93" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌍</v>
-      </c>
-    </row>
-    <row r="94" spans="2:16">
-      <c r="B94" t="str">
-        <f t="shared" si="10"/>
         <v>1D30E</v>
       </c>
       <c r="C94" cm="1">
@@ -14330,7 +15066,7 @@
         <v>9</v>
       </c>
       <c r="F94" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌎</v>
       </c>
       <c r="H94" s="1" t="s">
@@ -14359,29 +15095,37 @@
         <v>7799</v>
       </c>
       <c r="L94" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚊𝌀𝌀</v>
+      </c>
+      <c r="M94" t="str">
+        <f t="shared" si="20"/>
+        <v>𝌎</v>
+      </c>
+      <c r="N94" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚊𝌀𝌀</v>
-      </c>
-      <c r="M94" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌎</v>
-      </c>
-      <c r="N94" t="str">
-        <f t="shared" si="12"/>
         <v>𤕠</v>
       </c>
       <c r="O94" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌎𤕠</v>
+      </c>
+      <c r="P94" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌎p</v>
+      </c>
+      <c r="Q94" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌎&lt;rt&gt;&amp;#x202E;𤕠&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R94" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌎q</v>
+      </c>
+    </row>
+    <row r="95" spans="2:18">
+      <c r="B95" t="str">
         <f t="shared" si="13"/>
-        <v>𝌎𤕠</v>
-      </c>
-      <c r="P94" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌎</v>
-      </c>
-    </row>
-    <row r="95" spans="2:16">
-      <c r="B95" t="str">
-        <f t="shared" si="10"/>
         <v>1D30F</v>
       </c>
       <c r="C95" cm="1">
@@ -14395,7 +15139,7 @@
         <v>10</v>
       </c>
       <c r="F95" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌏</v>
       </c>
       <c r="H95" t="s">
@@ -14423,29 +15167,37 @@
         <v>7877</v>
       </c>
       <c r="L95" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚋⚊⚊</v>
+      </c>
+      <c r="M95" t="str">
+        <f t="shared" si="20"/>
+        <v>𝌏</v>
+      </c>
+      <c r="N95" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚋⚊⚊</v>
-      </c>
-      <c r="M95" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌏</v>
-      </c>
-      <c r="N95" t="str">
-        <f t="shared" si="12"/>
         <v>羨</v>
       </c>
       <c r="O95" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌏羨</v>
+      </c>
+      <c r="P95" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌏p</v>
+      </c>
+      <c r="Q95" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌏&lt;rt&gt;&amp;#x202E;羨&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R95" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌏q</v>
+      </c>
+    </row>
+    <row r="96" spans="2:18">
+      <c r="B96" t="str">
         <f t="shared" si="13"/>
-        <v>𝌏羨</v>
-      </c>
-      <c r="P95" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌏</v>
-      </c>
-    </row>
-    <row r="96" spans="2:16">
-      <c r="B96" t="str">
-        <f t="shared" si="10"/>
         <v>1D310</v>
       </c>
       <c r="C96" cm="1">
@@ -14459,7 +15211,7 @@
         <v>11</v>
       </c>
       <c r="F96" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌐</v>
       </c>
       <c r="H96" t="s">
@@ -14487,29 +15239,37 @@
         <v>7878</v>
       </c>
       <c r="L96" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚋⚊⚋</v>
+      </c>
+      <c r="M96" t="str">
+        <f t="shared" si="20"/>
+        <v>𝌐</v>
+      </c>
+      <c r="N96" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚋⚊⚋</v>
-      </c>
-      <c r="M96" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌐</v>
-      </c>
-      <c r="N96" t="str">
-        <f t="shared" si="12"/>
         <v>差</v>
       </c>
       <c r="O96" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌐差</v>
+      </c>
+      <c r="P96" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌐p</v>
+      </c>
+      <c r="Q96" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌐&lt;rt&gt;&amp;#x202E;差&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R96" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌐q</v>
+      </c>
+    </row>
+    <row r="97" spans="2:18">
+      <c r="B97" t="str">
         <f t="shared" si="13"/>
-        <v>𝌐差</v>
-      </c>
-      <c r="P96" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌐</v>
-      </c>
-    </row>
-    <row r="97" spans="2:16">
-      <c r="B97" t="str">
-        <f t="shared" si="10"/>
         <v>1D311</v>
       </c>
       <c r="C97" cm="1">
@@ -14523,7 +15283,7 @@
         <v>12</v>
       </c>
       <c r="F97" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌑</v>
       </c>
       <c r="H97" t="s">
@@ -14551,29 +15311,37 @@
         <v>7879</v>
       </c>
       <c r="L97" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚋⚊𝌀</v>
+      </c>
+      <c r="M97" t="str">
+        <f t="shared" si="20"/>
+        <v>𝌑</v>
+      </c>
+      <c r="N97" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚋⚊𝌀</v>
-      </c>
-      <c r="M97" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌑</v>
-      </c>
-      <c r="N97" t="str">
-        <f t="shared" si="12"/>
         <v>童</v>
       </c>
       <c r="O97" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌑童</v>
+      </c>
+      <c r="P97" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌑p</v>
+      </c>
+      <c r="Q97" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌑&lt;rt&gt;&amp;#x202E;童&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R97" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌑q</v>
+      </c>
+    </row>
+    <row r="98" spans="2:18">
+      <c r="B98" t="str">
         <f t="shared" si="13"/>
-        <v>𝌑童</v>
-      </c>
-      <c r="P97" t="str">
-        <f t="shared" si="14"/>
-        <v>𝌑</v>
-      </c>
-    </row>
-    <row r="98" spans="2:16">
-      <c r="B98" t="str">
-        <f t="shared" si="10"/>
         <v>1D312</v>
       </c>
       <c r="C98" cm="1">
@@ -14587,7 +15355,7 @@
         <v>13</v>
       </c>
       <c r="F98" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌒</v>
       </c>
       <c r="H98" t="s">
@@ -14615,29 +15383,37 @@
         <v>7887</v>
       </c>
       <c r="L98" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚋⚋⚊</v>
+      </c>
+      <c r="M98" t="str">
+        <f t="shared" ref="M98:M113" si="22">_xlfn.UNICHAR($C98)</f>
+        <v>𝌒</v>
+      </c>
+      <c r="N98" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚋⚋⚊</v>
-      </c>
-      <c r="M98" t="str">
-        <f t="shared" ref="M98:P113" si="16">_xlfn.UNICHAR($C98)</f>
-        <v>𝌒</v>
-      </c>
-      <c r="N98" t="str">
-        <f t="shared" si="12"/>
         <v>增</v>
       </c>
       <c r="O98" t="str">
+        <f t="shared" si="16"/>
+        <v>𝌒增</v>
+      </c>
+      <c r="P98" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌒p</v>
+      </c>
+      <c r="Q98" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌒&lt;rt&gt;&amp;#x202E;增&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R98" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌒q</v>
+      </c>
+    </row>
+    <row r="99" spans="2:18">
+      <c r="B99" t="str">
         <f t="shared" si="13"/>
-        <v>𝌒增</v>
-      </c>
-      <c r="P98" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌒</v>
-      </c>
-    </row>
-    <row r="99" spans="2:16">
-      <c r="B99" t="str">
-        <f t="shared" si="10"/>
         <v>1D313</v>
       </c>
       <c r="C99" cm="1">
@@ -14651,7 +15427,7 @@
         <v>14</v>
       </c>
       <c r="F99" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌓</v>
       </c>
       <c r="H99" t="s">
@@ -14679,29 +15455,37 @@
         <v>7888</v>
       </c>
       <c r="L99" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚋⚋⚋</v>
+      </c>
+      <c r="M99" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌓</v>
+      </c>
+      <c r="N99" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚋⚋⚋</v>
-      </c>
-      <c r="M99" t="str">
+        <v>銳</v>
+      </c>
+      <c r="O99" t="str">
         <f t="shared" si="16"/>
-        <v>𝌓</v>
-      </c>
-      <c r="N99" t="str">
-        <f t="shared" si="12"/>
-        <v>銳</v>
-      </c>
-      <c r="O99" t="str">
+        <v>𝌓銳</v>
+      </c>
+      <c r="P99" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌓p</v>
+      </c>
+      <c r="Q99" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌓&lt;rt&gt;&amp;#x202E;銳&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R99" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌓q</v>
+      </c>
+    </row>
+    <row r="100" spans="2:18">
+      <c r="B100" t="str">
         <f t="shared" si="13"/>
-        <v>𝌓銳</v>
-      </c>
-      <c r="P99" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌓</v>
-      </c>
-    </row>
-    <row r="100" spans="2:16">
-      <c r="B100" t="str">
-        <f t="shared" si="10"/>
         <v>1D314</v>
       </c>
       <c r="C100" cm="1">
@@ -14715,7 +15499,7 @@
         <v>15</v>
       </c>
       <c r="F100" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌔</v>
       </c>
       <c r="H100" t="s">
@@ -14743,29 +15527,37 @@
         <v>7889</v>
       </c>
       <c r="L100" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚋⚋𝌀</v>
+      </c>
+      <c r="M100" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌔</v>
+      </c>
+      <c r="N100" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚋⚋𝌀</v>
-      </c>
-      <c r="M100" t="str">
+        <v>達</v>
+      </c>
+      <c r="O100" t="str">
         <f t="shared" si="16"/>
-        <v>𝌔</v>
-      </c>
-      <c r="N100" t="str">
-        <f t="shared" si="12"/>
-        <v>達</v>
-      </c>
-      <c r="O100" t="str">
+        <v>𝌔達</v>
+      </c>
+      <c r="P100" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌔p</v>
+      </c>
+      <c r="Q100" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌔&lt;rt&gt;&amp;#x202E;達&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R100" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌔q</v>
+      </c>
+    </row>
+    <row r="101" spans="2:18">
+      <c r="B101" t="str">
         <f t="shared" si="13"/>
-        <v>𝌔達</v>
-      </c>
-      <c r="P100" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌔</v>
-      </c>
-    </row>
-    <row r="101" spans="2:16">
-      <c r="B101" t="str">
-        <f t="shared" si="10"/>
         <v>1D315</v>
       </c>
       <c r="C101" cm="1">
@@ -14779,7 +15571,7 @@
         <v>16</v>
       </c>
       <c r="F101" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌕</v>
       </c>
       <c r="H101" t="s">
@@ -14807,29 +15599,37 @@
         <v>7897</v>
       </c>
       <c r="L101" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚋𝌀⚊</v>
+      </c>
+      <c r="M101" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌕</v>
+      </c>
+      <c r="N101" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚋𝌀⚊</v>
-      </c>
-      <c r="M101" t="str">
+        <v>交</v>
+      </c>
+      <c r="O101" t="str">
         <f t="shared" si="16"/>
-        <v>𝌕</v>
-      </c>
-      <c r="N101" t="str">
-        <f t="shared" si="12"/>
-        <v>交</v>
-      </c>
-      <c r="O101" t="str">
+        <v>𝌕交</v>
+      </c>
+      <c r="P101" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌕p</v>
+      </c>
+      <c r="Q101" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌕&lt;rt&gt;&amp;#x202E;交&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R101" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌕q</v>
+      </c>
+    </row>
+    <row r="102" spans="2:18">
+      <c r="B102" t="str">
         <f t="shared" si="13"/>
-        <v>𝌕交</v>
-      </c>
-      <c r="P101" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌕</v>
-      </c>
-    </row>
-    <row r="102" spans="2:16">
-      <c r="B102" t="str">
-        <f t="shared" si="10"/>
         <v>1D316</v>
       </c>
       <c r="C102" cm="1">
@@ -14843,7 +15643,7 @@
         <v>17</v>
       </c>
       <c r="F102" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌖</v>
       </c>
       <c r="H102" t="s">
@@ -14871,29 +15671,37 @@
         <v>7898</v>
       </c>
       <c r="L102" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚋𝌀⚋</v>
+      </c>
+      <c r="M102" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌖</v>
+      </c>
+      <c r="N102" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚋𝌀⚋</v>
-      </c>
-      <c r="M102" t="str">
+        <v>䎡</v>
+      </c>
+      <c r="O102" t="str">
         <f t="shared" si="16"/>
-        <v>𝌖</v>
-      </c>
-      <c r="N102" t="str">
-        <f t="shared" si="12"/>
-        <v>䎡</v>
-      </c>
-      <c r="O102" t="str">
+        <v>𝌖䎡</v>
+      </c>
+      <c r="P102" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌖p</v>
+      </c>
+      <c r="Q102" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌖&lt;rt&gt;&amp;#x202E;䎡&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R102" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌖q</v>
+      </c>
+    </row>
+    <row r="103" spans="2:18">
+      <c r="B103" t="str">
         <f t="shared" si="13"/>
-        <v>𝌖䎡</v>
-      </c>
-      <c r="P102" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌖</v>
-      </c>
-    </row>
-    <row r="103" spans="2:16">
-      <c r="B103" t="str">
-        <f t="shared" si="10"/>
         <v>1D317</v>
       </c>
       <c r="C103" cm="1">
@@ -14907,7 +15715,7 @@
         <v>18</v>
       </c>
       <c r="F103" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌗</v>
       </c>
       <c r="H103" t="s">
@@ -14935,29 +15743,37 @@
         <v>7899</v>
       </c>
       <c r="L103" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊⚋𝌀𝌀</v>
+      </c>
+      <c r="M103" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌗</v>
+      </c>
+      <c r="N103" t="str">
         <f t="shared" si="15"/>
-        <v>⚊⚋𝌀𝌀</v>
-      </c>
-      <c r="M103" t="str">
+        <v>傒</v>
+      </c>
+      <c r="O103" t="str">
         <f t="shared" si="16"/>
-        <v>𝌗</v>
-      </c>
-      <c r="N103" t="str">
-        <f t="shared" si="12"/>
-        <v>傒</v>
-      </c>
-      <c r="O103" t="str">
+        <v>𝌗傒</v>
+      </c>
+      <c r="P103" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌗p</v>
+      </c>
+      <c r="Q103" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌗&lt;rt&gt;&amp;#x202E;傒&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R103" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌗q</v>
+      </c>
+    </row>
+    <row r="104" spans="2:18">
+      <c r="B104" t="str">
         <f t="shared" si="13"/>
-        <v>𝌗傒</v>
-      </c>
-      <c r="P103" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌗</v>
-      </c>
-    </row>
-    <row r="104" spans="2:16">
-      <c r="B104" t="str">
-        <f t="shared" si="10"/>
         <v>1D318</v>
       </c>
       <c r="C104" cm="1">
@@ -14971,7 +15787,7 @@
         <v>19</v>
       </c>
       <c r="F104" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌘</v>
       </c>
       <c r="H104" t="s">
@@ -14999,29 +15815,37 @@
         <v>7977</v>
       </c>
       <c r="L104" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊𝌀⚊⚊</v>
+      </c>
+      <c r="M104" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌘</v>
+      </c>
+      <c r="N104" t="str">
         <f t="shared" si="15"/>
-        <v>⚊𝌀⚊⚊</v>
-      </c>
-      <c r="M104" t="str">
+        <v>從</v>
+      </c>
+      <c r="O104" t="str">
         <f t="shared" si="16"/>
-        <v>𝌘</v>
-      </c>
-      <c r="N104" t="str">
-        <f t="shared" si="12"/>
-        <v>從</v>
-      </c>
-      <c r="O104" t="str">
+        <v>𝌘從</v>
+      </c>
+      <c r="P104" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌘p</v>
+      </c>
+      <c r="Q104" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌘&lt;rt&gt;&amp;#x202E;從&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R104" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌘q</v>
+      </c>
+    </row>
+    <row r="105" spans="2:18">
+      <c r="B105" t="str">
         <f t="shared" si="13"/>
-        <v>𝌘從</v>
-      </c>
-      <c r="P104" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌘</v>
-      </c>
-    </row>
-    <row r="105" spans="2:16">
-      <c r="B105" t="str">
-        <f t="shared" si="10"/>
         <v>1D319</v>
       </c>
       <c r="C105" cm="1">
@@ -15035,7 +15859,7 @@
         <v>20</v>
       </c>
       <c r="F105" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌙</v>
       </c>
       <c r="H105" t="s">
@@ -15063,29 +15887,37 @@
         <v>7978</v>
       </c>
       <c r="L105" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊𝌀⚊⚋</v>
+      </c>
+      <c r="M105" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌙</v>
+      </c>
+      <c r="N105" t="str">
         <f t="shared" si="15"/>
-        <v>⚊𝌀⚊⚋</v>
-      </c>
-      <c r="M105" t="str">
+        <v>進</v>
+      </c>
+      <c r="O105" t="str">
         <f t="shared" si="16"/>
-        <v>𝌙</v>
-      </c>
-      <c r="N105" t="str">
-        <f t="shared" si="12"/>
-        <v>進</v>
-      </c>
-      <c r="O105" t="str">
+        <v>𝌙進</v>
+      </c>
+      <c r="P105" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌙p</v>
+      </c>
+      <c r="Q105" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌙&lt;rt&gt;&amp;#x202E;進&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R105" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌙q</v>
+      </c>
+    </row>
+    <row r="106" spans="2:18">
+      <c r="B106" t="str">
         <f t="shared" si="13"/>
-        <v>𝌙進</v>
-      </c>
-      <c r="P105" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌙</v>
-      </c>
-    </row>
-    <row r="106" spans="2:16">
-      <c r="B106" t="str">
-        <f t="shared" si="10"/>
         <v>1D31A</v>
       </c>
       <c r="C106" cm="1">
@@ -15099,7 +15931,7 @@
         <v>21</v>
       </c>
       <c r="F106" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌚</v>
       </c>
       <c r="H106" t="s">
@@ -15127,29 +15959,37 @@
         <v>7979</v>
       </c>
       <c r="L106" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊𝌀⚊𝌀</v>
+      </c>
+      <c r="M106" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌚</v>
+      </c>
+      <c r="N106" t="str">
         <f t="shared" si="15"/>
-        <v>⚊𝌀⚊𝌀</v>
-      </c>
-      <c r="M106" t="str">
+        <v>釋</v>
+      </c>
+      <c r="O106" t="str">
         <f t="shared" si="16"/>
-        <v>𝌚</v>
-      </c>
-      <c r="N106" t="str">
-        <f t="shared" si="12"/>
-        <v>釋</v>
-      </c>
-      <c r="O106" t="str">
+        <v>𝌚釋</v>
+      </c>
+      <c r="P106" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌚p</v>
+      </c>
+      <c r="Q106" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌚&lt;rt&gt;&amp;#x202E;釋&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R106" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌚q</v>
+      </c>
+    </row>
+    <row r="107" spans="2:18">
+      <c r="B107" t="str">
         <f t="shared" si="13"/>
-        <v>𝌚釋</v>
-      </c>
-      <c r="P106" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌚</v>
-      </c>
-    </row>
-    <row r="107" spans="2:16">
-      <c r="B107" t="str">
-        <f t="shared" si="10"/>
         <v>1D31B</v>
       </c>
       <c r="C107" cm="1">
@@ -15163,7 +16003,7 @@
         <v>22</v>
       </c>
       <c r="F107" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌛</v>
       </c>
       <c r="H107" t="s">
@@ -15191,29 +16031,37 @@
         <v>7987</v>
       </c>
       <c r="L107" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊𝌀⚋⚊</v>
+      </c>
+      <c r="M107" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌛</v>
+      </c>
+      <c r="N107" t="str">
         <f t="shared" si="15"/>
-        <v>⚊𝌀⚋⚊</v>
-      </c>
-      <c r="M107" t="str">
+        <v>格</v>
+      </c>
+      <c r="O107" t="str">
         <f t="shared" si="16"/>
-        <v>𝌛</v>
-      </c>
-      <c r="N107" t="str">
-        <f t="shared" si="12"/>
-        <v>格</v>
-      </c>
-      <c r="O107" t="str">
+        <v>𝌛格</v>
+      </c>
+      <c r="P107" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌛p</v>
+      </c>
+      <c r="Q107" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌛&lt;rt&gt;&amp;#x202E;格&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R107" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌛q</v>
+      </c>
+    </row>
+    <row r="108" spans="2:18">
+      <c r="B108" t="str">
         <f t="shared" si="13"/>
-        <v>𝌛格</v>
-      </c>
-      <c r="P107" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌛</v>
-      </c>
-    </row>
-    <row r="108" spans="2:16">
-      <c r="B108" t="str">
-        <f t="shared" si="10"/>
         <v>1D31C</v>
       </c>
       <c r="C108" cm="1">
@@ -15227,7 +16075,7 @@
         <v>23</v>
       </c>
       <c r="F108" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌜</v>
       </c>
       <c r="H108" t="s">
@@ -15255,29 +16103,37 @@
         <v>7988</v>
       </c>
       <c r="L108" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊𝌀⚋⚋</v>
+      </c>
+      <c r="M108" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌜</v>
+      </c>
+      <c r="N108" t="str">
         <f t="shared" si="15"/>
-        <v>⚊𝌀⚋⚋</v>
-      </c>
-      <c r="M108" t="str">
+        <v>夷</v>
+      </c>
+      <c r="O108" t="str">
         <f t="shared" si="16"/>
-        <v>𝌜</v>
-      </c>
-      <c r="N108" t="str">
-        <f t="shared" si="12"/>
-        <v>夷</v>
-      </c>
-      <c r="O108" t="str">
+        <v>𝌜夷</v>
+      </c>
+      <c r="P108" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌜p</v>
+      </c>
+      <c r="Q108" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌜&lt;rt&gt;&amp;#x202E;夷&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R108" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌜q</v>
+      </c>
+    </row>
+    <row r="109" spans="2:18">
+      <c r="B109" t="str">
         <f t="shared" si="13"/>
-        <v>𝌜夷</v>
-      </c>
-      <c r="P108" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌜</v>
-      </c>
-    </row>
-    <row r="109" spans="2:16">
-      <c r="B109" t="str">
-        <f t="shared" si="10"/>
         <v>1D31D</v>
       </c>
       <c r="C109" cm="1">
@@ -15291,7 +16147,7 @@
         <v>24</v>
       </c>
       <c r="F109" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌝</v>
       </c>
       <c r="H109" t="s">
@@ -15319,29 +16175,37 @@
         <v>7989</v>
       </c>
       <c r="L109" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊𝌀⚋𝌀</v>
+      </c>
+      <c r="M109" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌝</v>
+      </c>
+      <c r="N109" t="str">
         <f t="shared" si="15"/>
-        <v>⚊𝌀⚋𝌀</v>
-      </c>
-      <c r="M109" t="str">
+        <v>樂</v>
+      </c>
+      <c r="O109" t="str">
         <f t="shared" si="16"/>
-        <v>𝌝</v>
-      </c>
-      <c r="N109" t="str">
-        <f t="shared" si="12"/>
-        <v>樂</v>
-      </c>
-      <c r="O109" t="str">
+        <v>𝌝樂</v>
+      </c>
+      <c r="P109" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌝p</v>
+      </c>
+      <c r="Q109" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌝&lt;rt&gt;&amp;#x202E;樂&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R109" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌝q</v>
+      </c>
+    </row>
+    <row r="110" spans="2:18">
+      <c r="B110" t="str">
         <f t="shared" si="13"/>
-        <v>𝌝樂</v>
-      </c>
-      <c r="P109" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌝</v>
-      </c>
-    </row>
-    <row r="110" spans="2:16">
-      <c r="B110" t="str">
-        <f t="shared" si="10"/>
         <v>1D31E</v>
       </c>
       <c r="C110" cm="1">
@@ -15355,7 +16219,7 @@
         <v>25</v>
       </c>
       <c r="F110" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌞</v>
       </c>
       <c r="H110" t="s">
@@ -15383,29 +16247,37 @@
         <v>7997</v>
       </c>
       <c r="L110" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊𝌀𝌀⚊</v>
+      </c>
+      <c r="M110" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌞</v>
+      </c>
+      <c r="N110" t="str">
         <f t="shared" si="15"/>
-        <v>⚊𝌀𝌀⚊</v>
-      </c>
-      <c r="M110" t="str">
+        <v>爭</v>
+      </c>
+      <c r="O110" t="str">
         <f t="shared" si="16"/>
-        <v>𝌞</v>
-      </c>
-      <c r="N110" t="str">
-        <f t="shared" si="12"/>
-        <v>爭</v>
-      </c>
-      <c r="O110" t="str">
+        <v>𝌞爭</v>
+      </c>
+      <c r="P110" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌞p</v>
+      </c>
+      <c r="Q110" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌞&lt;rt&gt;&amp;#x202E;爭&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R110" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌞q</v>
+      </c>
+    </row>
+    <row r="111" spans="2:18">
+      <c r="B111" t="str">
         <f t="shared" si="13"/>
-        <v>𝌞爭</v>
-      </c>
-      <c r="P110" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌞</v>
-      </c>
-    </row>
-    <row r="111" spans="2:16">
-      <c r="B111" t="str">
-        <f t="shared" si="10"/>
         <v>1D31F</v>
       </c>
       <c r="C111" cm="1">
@@ -15419,7 +16291,7 @@
         <v>26</v>
       </c>
       <c r="F111" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌟</v>
       </c>
       <c r="H111" t="s">
@@ -15447,29 +16319,37 @@
         <v>7998</v>
       </c>
       <c r="L111" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊𝌀𝌀⚋</v>
+      </c>
+      <c r="M111" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌟</v>
+      </c>
+      <c r="N111" t="str">
         <f t="shared" si="15"/>
-        <v>⚊𝌀𝌀⚋</v>
-      </c>
-      <c r="M111" t="str">
+        <v>務</v>
+      </c>
+      <c r="O111" t="str">
         <f t="shared" si="16"/>
-        <v>𝌟</v>
-      </c>
-      <c r="N111" t="str">
-        <f t="shared" si="12"/>
-        <v>務</v>
-      </c>
-      <c r="O111" t="str">
+        <v>𝌟務</v>
+      </c>
+      <c r="P111" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌟p</v>
+      </c>
+      <c r="Q111" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌟&lt;rt&gt;&amp;#x202E;務&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R111" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌟q</v>
+      </c>
+    </row>
+    <row r="112" spans="2:18">
+      <c r="B112" t="str">
         <f t="shared" si="13"/>
-        <v>𝌟務</v>
-      </c>
-      <c r="P111" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌟</v>
-      </c>
-    </row>
-    <row r="112" spans="2:16">
-      <c r="B112" t="str">
-        <f t="shared" si="10"/>
         <v>1D320</v>
       </c>
       <c r="C112" cm="1">
@@ -15483,7 +16363,7 @@
         <v>27</v>
       </c>
       <c r="F112" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌠</v>
       </c>
       <c r="H112" t="s">
@@ -15511,29 +16391,37 @@
         <v>7999</v>
       </c>
       <c r="L112" t="str">
+        <f t="shared" si="21"/>
+        <v>⚊𝌀𝌀𝌀</v>
+      </c>
+      <c r="M112" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌠</v>
+      </c>
+      <c r="N112" t="str">
         <f t="shared" si="15"/>
-        <v>⚊𝌀𝌀𝌀</v>
-      </c>
-      <c r="M112" t="str">
+        <v>事</v>
+      </c>
+      <c r="O112" t="str">
         <f t="shared" si="16"/>
-        <v>𝌠</v>
-      </c>
-      <c r="N112" t="str">
-        <f t="shared" si="12"/>
-        <v>事</v>
-      </c>
-      <c r="O112" t="str">
+        <v>𝌠事</v>
+      </c>
+      <c r="P112" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌠p</v>
+      </c>
+      <c r="Q112" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌠&lt;rt&gt;&amp;#x202E;事&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R112" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌠q</v>
+      </c>
+    </row>
+    <row r="113" spans="2:18">
+      <c r="B113" t="str">
         <f t="shared" si="13"/>
-        <v>𝌠事</v>
-      </c>
-      <c r="P112" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌠</v>
-      </c>
-    </row>
-    <row r="113" spans="2:16">
-      <c r="B113" t="str">
-        <f t="shared" si="10"/>
         <v>1D321</v>
       </c>
       <c r="C113" cm="1">
@@ -15547,7 +16435,7 @@
         <v>28</v>
       </c>
       <c r="F113" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌡</v>
       </c>
       <c r="H113" t="s">
@@ -15575,29 +16463,37 @@
         <v>8777</v>
       </c>
       <c r="L113" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚊⚊⚊</v>
+      </c>
+      <c r="M113" t="str">
+        <f t="shared" si="22"/>
+        <v>𝌡</v>
+      </c>
+      <c r="N113" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚊⚊⚊</v>
-      </c>
-      <c r="M113" t="str">
+        <v>更</v>
+      </c>
+      <c r="O113" t="str">
         <f t="shared" si="16"/>
-        <v>𝌡</v>
-      </c>
-      <c r="N113" t="str">
-        <f t="shared" si="12"/>
-        <v>更</v>
-      </c>
-      <c r="O113" t="str">
+        <v>𝌡更</v>
+      </c>
+      <c r="P113" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌡p</v>
+      </c>
+      <c r="Q113" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌡&lt;rt&gt;&amp;#x202E;更&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R113" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌡q</v>
+      </c>
+    </row>
+    <row r="114" spans="2:18">
+      <c r="B114" t="str">
         <f t="shared" si="13"/>
-        <v>𝌡更</v>
-      </c>
-      <c r="P113" t="str">
-        <f t="shared" si="16"/>
-        <v>𝌡</v>
-      </c>
-    </row>
-    <row r="114" spans="2:16">
-      <c r="B114" t="str">
-        <f t="shared" si="10"/>
         <v>1D322</v>
       </c>
       <c r="C114" cm="1">
@@ -15611,7 +16507,7 @@
         <v>29</v>
       </c>
       <c r="F114" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌢</v>
       </c>
       <c r="H114" t="s">
@@ -15639,29 +16535,37 @@
         <v>8778</v>
       </c>
       <c r="L114" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚊⚊⚋</v>
+      </c>
+      <c r="M114" t="str">
+        <f t="shared" ref="M114:M129" si="23">_xlfn.UNICHAR($C114)</f>
+        <v>𝌢</v>
+      </c>
+      <c r="N114" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚊⚊⚋</v>
-      </c>
-      <c r="M114" t="str">
-        <f t="shared" ref="M114:P129" si="17">_xlfn.UNICHAR($C114)</f>
-        <v>𝌢</v>
-      </c>
-      <c r="N114" t="str">
-        <f t="shared" si="12"/>
         <v>斷</v>
       </c>
       <c r="O114" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌢斷</v>
       </c>
       <c r="P114" t="str">
         <f t="shared" si="17"/>
-        <v>𝌢</v>
-      </c>
-    </row>
-    <row r="115" spans="2:16">
+        <v>𝌢p</v>
+      </c>
+      <c r="Q114" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌢&lt;rt&gt;&amp;#x202E;斷&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R114" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌢q</v>
+      </c>
+    </row>
+    <row r="115" spans="2:18">
       <c r="B115" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D323</v>
       </c>
       <c r="C115" cm="1">
@@ -15675,7 +16579,7 @@
         <v>30</v>
       </c>
       <c r="F115" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌣</v>
       </c>
       <c r="H115" t="s">
@@ -15703,29 +16607,37 @@
         <v>8779</v>
       </c>
       <c r="L115" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚊⚊𝌀</v>
+      </c>
+      <c r="M115" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌣</v>
+      </c>
+      <c r="N115" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚊⚊𝌀</v>
-      </c>
-      <c r="M115" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌣</v>
-      </c>
-      <c r="N115" t="str">
-        <f t="shared" si="12"/>
         <v>毅</v>
       </c>
       <c r="O115" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌣毅</v>
       </c>
       <c r="P115" t="str">
         <f t="shared" si="17"/>
-        <v>𝌣</v>
-      </c>
-    </row>
-    <row r="116" spans="2:16">
+        <v>𝌣p</v>
+      </c>
+      <c r="Q115" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌣&lt;rt&gt;&amp;#x202E;毅&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R115" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌣q</v>
+      </c>
+    </row>
+    <row r="116" spans="2:18">
       <c r="B116" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D324</v>
       </c>
       <c r="C116" cm="1">
@@ -15739,7 +16651,7 @@
         <v>31</v>
       </c>
       <c r="F116" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌤</v>
       </c>
       <c r="H116" t="s">
@@ -15767,29 +16679,37 @@
         <v>8787</v>
       </c>
       <c r="L116" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚊⚋⚊</v>
+      </c>
+      <c r="M116" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌤</v>
+      </c>
+      <c r="N116" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚊⚋⚊</v>
-      </c>
-      <c r="M116" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌤</v>
-      </c>
-      <c r="N116" t="str">
-        <f t="shared" si="12"/>
         <v>裝</v>
       </c>
       <c r="O116" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌤裝</v>
       </c>
       <c r="P116" t="str">
         <f t="shared" si="17"/>
-        <v>𝌤</v>
-      </c>
-    </row>
-    <row r="117" spans="2:16">
+        <v>𝌤p</v>
+      </c>
+      <c r="Q116" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌤&lt;rt&gt;&amp;#x202E;裝&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R116" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌤q</v>
+      </c>
+    </row>
+    <row r="117" spans="2:18">
       <c r="B117" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D325</v>
       </c>
       <c r="C117" cm="1">
@@ -15803,7 +16723,7 @@
         <v>32</v>
       </c>
       <c r="F117" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌥</v>
       </c>
       <c r="H117" t="s">
@@ -15831,29 +16751,37 @@
         <v>8788</v>
       </c>
       <c r="L117" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚊⚋⚋</v>
+      </c>
+      <c r="M117" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌥</v>
+      </c>
+      <c r="N117" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚊⚋⚋</v>
-      </c>
-      <c r="M117" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌥</v>
-      </c>
-      <c r="N117" t="str">
-        <f t="shared" si="12"/>
         <v>眾</v>
       </c>
       <c r="O117" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌥眾</v>
       </c>
       <c r="P117" t="str">
         <f t="shared" si="17"/>
-        <v>𝌥</v>
-      </c>
-    </row>
-    <row r="118" spans="2:16">
+        <v>𝌥p</v>
+      </c>
+      <c r="Q117" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌥&lt;rt&gt;&amp;#x202E;眾&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R117" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌥q</v>
+      </c>
+    </row>
+    <row r="118" spans="2:18">
       <c r="B118" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D326</v>
       </c>
       <c r="C118" cm="1">
@@ -15867,7 +16795,7 @@
         <v>33</v>
       </c>
       <c r="F118" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌦</v>
       </c>
       <c r="H118" t="s">
@@ -15895,29 +16823,37 @@
         <v>8789</v>
       </c>
       <c r="L118" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚊⚋𝌀</v>
+      </c>
+      <c r="M118" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌦</v>
+      </c>
+      <c r="N118" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚊⚋𝌀</v>
-      </c>
-      <c r="M118" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌦</v>
-      </c>
-      <c r="N118" t="str">
-        <f t="shared" si="12"/>
         <v>密</v>
       </c>
       <c r="O118" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌦密</v>
       </c>
       <c r="P118" t="str">
         <f t="shared" si="17"/>
-        <v>𝌦</v>
-      </c>
-    </row>
-    <row r="119" spans="2:16">
+        <v>𝌦p</v>
+      </c>
+      <c r="Q118" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌦&lt;rt&gt;&amp;#x202E;密&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R118" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌦q</v>
+      </c>
+    </row>
+    <row r="119" spans="2:18">
       <c r="B119" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D327</v>
       </c>
       <c r="C119" cm="1">
@@ -15931,7 +16867,7 @@
         <v>34</v>
       </c>
       <c r="F119" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌧</v>
       </c>
       <c r="H119" t="s">
@@ -15959,29 +16895,37 @@
         <v>8797</v>
       </c>
       <c r="L119" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚊𝌀⚊</v>
+      </c>
+      <c r="M119" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌧</v>
+      </c>
+      <c r="N119" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚊𝌀⚊</v>
-      </c>
-      <c r="M119" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌧</v>
-      </c>
-      <c r="N119" t="str">
-        <f t="shared" si="12"/>
         <v>親</v>
       </c>
       <c r="O119" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌧親</v>
       </c>
       <c r="P119" t="str">
         <f t="shared" si="17"/>
-        <v>𝌧</v>
-      </c>
-    </row>
-    <row r="120" spans="2:16">
+        <v>𝌧p</v>
+      </c>
+      <c r="Q119" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌧&lt;rt&gt;&amp;#x202E;親&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R119" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌧q</v>
+      </c>
+    </row>
+    <row r="120" spans="2:18">
       <c r="B120" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D328</v>
       </c>
       <c r="C120" cm="1">
@@ -15995,7 +16939,7 @@
         <v>35</v>
       </c>
       <c r="F120" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌨</v>
       </c>
       <c r="H120" t="s">
@@ -16023,29 +16967,37 @@
         <v>8798</v>
       </c>
       <c r="L120" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚊𝌀⚋</v>
+      </c>
+      <c r="M120" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌨</v>
+      </c>
+      <c r="N120" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚊𝌀⚋</v>
-      </c>
-      <c r="M120" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌨</v>
-      </c>
-      <c r="N120" t="str">
-        <f t="shared" si="12"/>
         <v>斂</v>
       </c>
       <c r="O120" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌨斂</v>
       </c>
       <c r="P120" t="str">
         <f t="shared" si="17"/>
-        <v>𝌨</v>
-      </c>
-    </row>
-    <row r="121" spans="2:16">
+        <v>𝌨p</v>
+      </c>
+      <c r="Q120" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌨&lt;rt&gt;&amp;#x202E;斂&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R120" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌨q</v>
+      </c>
+    </row>
+    <row r="121" spans="2:18">
       <c r="B121" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D329</v>
       </c>
       <c r="C121" cm="1">
@@ -16059,7 +17011,7 @@
         <v>36</v>
       </c>
       <c r="F121" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌩</v>
       </c>
       <c r="H121" t="s">
@@ -16087,29 +17039,37 @@
         <v>8799</v>
       </c>
       <c r="L121" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚊𝌀𝌀</v>
+      </c>
+      <c r="M121" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌩</v>
+      </c>
+      <c r="N121" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚊𝌀𝌀</v>
-      </c>
-      <c r="M121" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌩</v>
-      </c>
-      <c r="N121" t="str">
-        <f t="shared" si="12"/>
         <v>彊</v>
       </c>
       <c r="O121" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌩彊</v>
       </c>
       <c r="P121" t="str">
         <f t="shared" si="17"/>
-        <v>𝌩</v>
-      </c>
-    </row>
-    <row r="122" spans="2:16">
+        <v>𝌩p</v>
+      </c>
+      <c r="Q121" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌩&lt;rt&gt;&amp;#x202E;彊&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R121" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌩q</v>
+      </c>
+    </row>
+    <row r="122" spans="2:18">
       <c r="B122" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D32A</v>
       </c>
       <c r="C122" cm="1">
@@ -16123,7 +17083,7 @@
         <v>37</v>
       </c>
       <c r="F122" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌪</v>
       </c>
       <c r="H122" t="s">
@@ -16151,29 +17111,37 @@
         <v>8877</v>
       </c>
       <c r="L122" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚋⚊⚊</v>
+      </c>
+      <c r="M122" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌪</v>
+      </c>
+      <c r="N122" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚋⚊⚊</v>
-      </c>
-      <c r="M122" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌪</v>
-      </c>
-      <c r="N122" t="str">
-        <f t="shared" si="12"/>
         <v>睟</v>
       </c>
       <c r="O122" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌪睟</v>
       </c>
       <c r="P122" t="str">
         <f t="shared" si="17"/>
-        <v>𝌪</v>
-      </c>
-    </row>
-    <row r="123" spans="2:16">
+        <v>𝌪p</v>
+      </c>
+      <c r="Q122" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌪&lt;rt&gt;&amp;#x202E;睟&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R122" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌪q</v>
+      </c>
+    </row>
+    <row r="123" spans="2:18">
       <c r="B123" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D32B</v>
       </c>
       <c r="C123" cm="1">
@@ -16187,7 +17155,7 @@
         <v>38</v>
       </c>
       <c r="F123" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌫</v>
       </c>
       <c r="H123" t="s">
@@ -16215,29 +17183,37 @@
         <v>8878</v>
       </c>
       <c r="L123" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚋⚊⚋</v>
+      </c>
+      <c r="M123" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌫</v>
+      </c>
+      <c r="N123" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚋⚊⚋</v>
-      </c>
-      <c r="M123" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌫</v>
-      </c>
-      <c r="N123" t="str">
-        <f t="shared" si="12"/>
         <v>盛</v>
       </c>
       <c r="O123" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌫盛</v>
       </c>
       <c r="P123" t="str">
         <f t="shared" si="17"/>
-        <v>𝌫</v>
-      </c>
-    </row>
-    <row r="124" spans="2:16">
+        <v>𝌫p</v>
+      </c>
+      <c r="Q123" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌫&lt;rt&gt;&amp;#x202E;盛&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R123" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌫q</v>
+      </c>
+    </row>
+    <row r="124" spans="2:18">
       <c r="B124" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D32C</v>
       </c>
       <c r="C124" cm="1">
@@ -16251,7 +17227,7 @@
         <v>39</v>
       </c>
       <c r="F124" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌬</v>
       </c>
       <c r="H124" t="s">
@@ -16279,29 +17255,37 @@
         <v>8879</v>
       </c>
       <c r="L124" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚋⚊𝌀</v>
+      </c>
+      <c r="M124" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌬</v>
+      </c>
+      <c r="N124" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚋⚊𝌀</v>
-      </c>
-      <c r="M124" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌬</v>
-      </c>
-      <c r="N124" t="str">
-        <f t="shared" si="12"/>
         <v>居</v>
       </c>
       <c r="O124" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌬居</v>
       </c>
       <c r="P124" t="str">
         <f t="shared" si="17"/>
-        <v>𝌬</v>
-      </c>
-    </row>
-    <row r="125" spans="2:16">
+        <v>𝌬p</v>
+      </c>
+      <c r="Q124" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌬&lt;rt&gt;&amp;#x202E;居&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R124" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌬q</v>
+      </c>
+    </row>
+    <row r="125" spans="2:18">
       <c r="B125" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D32D</v>
       </c>
       <c r="C125" cm="1">
@@ -16315,7 +17299,7 @@
         <v>40</v>
       </c>
       <c r="F125" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌭</v>
       </c>
       <c r="H125" t="s">
@@ -16343,29 +17327,37 @@
         <v>8887</v>
       </c>
       <c r="L125" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚋⚋⚊</v>
+      </c>
+      <c r="M125" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌭</v>
+      </c>
+      <c r="N125" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚋⚋⚊</v>
-      </c>
-      <c r="M125" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌭</v>
-      </c>
-      <c r="N125" t="str">
-        <f t="shared" si="12"/>
         <v>法</v>
       </c>
       <c r="O125" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌭法</v>
       </c>
       <c r="P125" t="str">
         <f t="shared" si="17"/>
-        <v>𝌭</v>
-      </c>
-    </row>
-    <row r="126" spans="2:16">
+        <v>𝌭p</v>
+      </c>
+      <c r="Q125" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌭&lt;rt&gt;&amp;#x202E;法&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R125" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌭q</v>
+      </c>
+    </row>
+    <row r="126" spans="2:18">
       <c r="B126" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D32E</v>
       </c>
       <c r="C126" cm="1">
@@ -16379,7 +17371,7 @@
         <v>41</v>
       </c>
       <c r="F126" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌮</v>
       </c>
       <c r="H126" t="s">
@@ -16407,29 +17399,37 @@
         <v>8888</v>
       </c>
       <c r="L126" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚋⚋⚋</v>
+      </c>
+      <c r="M126" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌮</v>
+      </c>
+      <c r="N126" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚋⚋⚋</v>
-      </c>
-      <c r="M126" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌮</v>
-      </c>
-      <c r="N126" t="str">
-        <f t="shared" si="12"/>
         <v>應</v>
       </c>
       <c r="O126" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌮應</v>
       </c>
       <c r="P126" t="str">
         <f t="shared" si="17"/>
-        <v>𝌮</v>
-      </c>
-    </row>
-    <row r="127" spans="2:16">
+        <v>𝌮p</v>
+      </c>
+      <c r="Q126" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌮&lt;rt&gt;&amp;#x202E;應&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R126" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌮q</v>
+      </c>
+    </row>
+    <row r="127" spans="2:18">
       <c r="B127" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D32F</v>
       </c>
       <c r="C127" cm="1">
@@ -16443,7 +17443,7 @@
         <v>42</v>
       </c>
       <c r="F127" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌯</v>
       </c>
       <c r="H127" t="s">
@@ -16471,29 +17471,37 @@
         <v>8889</v>
       </c>
       <c r="L127" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚋⚋𝌀</v>
+      </c>
+      <c r="M127" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌯</v>
+      </c>
+      <c r="N127" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚋⚋𝌀</v>
-      </c>
-      <c r="M127" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌯</v>
-      </c>
-      <c r="N127" t="str">
-        <f t="shared" si="12"/>
         <v>迎</v>
       </c>
       <c r="O127" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌯迎</v>
       </c>
       <c r="P127" t="str">
         <f t="shared" si="17"/>
-        <v>𝌯</v>
-      </c>
-    </row>
-    <row r="128" spans="2:16">
+        <v>𝌯p</v>
+      </c>
+      <c r="Q127" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌯&lt;rt&gt;&amp;#x202E;迎&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R127" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌯q</v>
+      </c>
+    </row>
+    <row r="128" spans="2:18">
       <c r="B128" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D330</v>
       </c>
       <c r="C128" cm="1">
@@ -16507,7 +17515,7 @@
         <v>43</v>
       </c>
       <c r="F128" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌰</v>
       </c>
       <c r="H128" t="s">
@@ -16535,29 +17543,37 @@
         <v>8897</v>
       </c>
       <c r="L128" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚋𝌀⚊</v>
+      </c>
+      <c r="M128" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌰</v>
+      </c>
+      <c r="N128" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚋𝌀⚊</v>
-      </c>
-      <c r="M128" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌰</v>
-      </c>
-      <c r="N128" t="str">
-        <f t="shared" si="12"/>
         <v>遇</v>
       </c>
       <c r="O128" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌰遇</v>
       </c>
       <c r="P128" t="str">
         <f t="shared" si="17"/>
-        <v>𝌰</v>
-      </c>
-    </row>
-    <row r="129" spans="2:16">
+        <v>𝌰p</v>
+      </c>
+      <c r="Q128" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌰&lt;rt&gt;&amp;#x202E;遇&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R128" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌰q</v>
+      </c>
+    </row>
+    <row r="129" spans="2:18">
       <c r="B129" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D331</v>
       </c>
       <c r="C129" cm="1">
@@ -16571,7 +17587,7 @@
         <v>44</v>
       </c>
       <c r="F129" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌱</v>
       </c>
       <c r="H129" t="s">
@@ -16599,29 +17615,37 @@
         <v>8898</v>
       </c>
       <c r="L129" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚋𝌀⚋</v>
+      </c>
+      <c r="M129" t="str">
+        <f t="shared" si="23"/>
+        <v>𝌱</v>
+      </c>
+      <c r="N129" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚋𝌀⚋</v>
-      </c>
-      <c r="M129" t="str">
-        <f t="shared" si="17"/>
-        <v>𝌱</v>
-      </c>
-      <c r="N129" t="str">
-        <f t="shared" si="12"/>
         <v>竈</v>
       </c>
       <c r="O129" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌱竈</v>
       </c>
       <c r="P129" t="str">
         <f t="shared" si="17"/>
-        <v>𝌱</v>
-      </c>
-    </row>
-    <row r="130" spans="2:16">
+        <v>𝌱p</v>
+      </c>
+      <c r="Q129" t="str">
+        <f t="shared" si="18"/>
+        <v>&lt;ruby&gt;𝌱&lt;rt&gt;&amp;#x202E;竈&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R129" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌱q</v>
+      </c>
+    </row>
+    <row r="130" spans="2:18">
       <c r="B130" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="13"/>
         <v>1D332</v>
       </c>
       <c r="C130" cm="1">
@@ -16635,7 +17659,7 @@
         <v>45</v>
       </c>
       <c r="F130" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌲</v>
       </c>
       <c r="H130" t="s">
@@ -16663,29 +17687,37 @@
         <v>8899</v>
       </c>
       <c r="L130" t="str">
+        <f t="shared" si="21"/>
+        <v>⚋⚋𝌀𝌀</v>
+      </c>
+      <c r="M130" t="str">
+        <f t="shared" ref="M130:M145" si="24">_xlfn.UNICHAR($C130)</f>
+        <v>𝌲</v>
+      </c>
+      <c r="N130" t="str">
         <f t="shared" si="15"/>
-        <v>⚋⚋𝌀𝌀</v>
-      </c>
-      <c r="M130" t="str">
-        <f t="shared" ref="M130:P145" si="18">_xlfn.UNICHAR($C130)</f>
-        <v>𝌲</v>
-      </c>
-      <c r="N130" t="str">
-        <f t="shared" si="12"/>
         <v>大</v>
       </c>
       <c r="O130" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="16"/>
         <v>𝌲大</v>
       </c>
       <c r="P130" t="str">
+        <f t="shared" si="17"/>
+        <v>𝌲p</v>
+      </c>
+      <c r="Q130" t="str">
         <f t="shared" si="18"/>
-        <v>𝌲</v>
-      </c>
-    </row>
-    <row r="131" spans="2:16">
+        <v>&lt;ruby&gt;𝌲&lt;rt&gt;&amp;#x202E;大&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R130" t="str">
+        <f t="shared" si="19"/>
+        <v>𝌲q</v>
+      </c>
+    </row>
+    <row r="131" spans="2:18">
       <c r="B131" t="str">
-        <f t="shared" ref="B131:B166" si="19">DEC2HEX($C131)</f>
+        <f t="shared" ref="B131:B166" si="25">DEC2HEX($C131)</f>
         <v>1D333</v>
       </c>
       <c r="C131" cm="1">
@@ -16699,7 +17731,7 @@
         <v>46</v>
       </c>
       <c r="F131" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌳</v>
       </c>
       <c r="H131" t="s">
@@ -16727,29 +17759,37 @@
         <v>8977</v>
       </c>
       <c r="L131" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>⚋𝌀⚊⚊</v>
       </c>
       <c r="M131" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌳</v>
       </c>
       <c r="N131" t="str">
-        <f t="shared" ref="N131:N166" si="20">IF($H131="",$G131,$H131)</f>
+        <f t="shared" ref="N131:N166" si="26">IF($H131="",$G131,$H131)</f>
         <v>廓</v>
       </c>
       <c r="O131" t="str">
-        <f t="shared" ref="O131:O166" si="21">M131&amp;N131</f>
+        <f t="shared" ref="O131:O166" si="27">M131&amp;N131</f>
         <v>𝌳廓</v>
       </c>
       <c r="P131" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌳</v>
-      </c>
-    </row>
-    <row r="132" spans="2:16">
+        <f t="shared" ref="P131:P166" si="28">_xlfn.UNICHAR($C131)&amp;"p"</f>
+        <v>𝌳p</v>
+      </c>
+      <c r="Q131" t="str">
+        <f t="shared" ref="Q131:Q166" si="29">"&lt;ruby&gt;"&amp;$M131&amp;"&lt;rt&gt;&amp;#x202E;"&amp;$N131&amp;"&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;"</f>
+        <v>&lt;ruby&gt;𝌳&lt;rt&gt;&amp;#x202E;廓&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R131" t="str">
+        <f t="shared" ref="R131:R166" si="30">_xlfn.UNICHAR($C131)&amp;"q"</f>
+        <v>𝌳q</v>
+      </c>
+    </row>
+    <row r="132" spans="2:18">
       <c r="B132" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D334</v>
       </c>
       <c r="C132" cm="1">
@@ -16763,7 +17803,7 @@
         <v>47</v>
       </c>
       <c r="F132" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌴</v>
       </c>
       <c r="H132" t="s">
@@ -16791,29 +17831,37 @@
         <v>8978</v>
       </c>
       <c r="L132" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>⚋𝌀⚊⚋</v>
       </c>
       <c r="M132" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌴</v>
       </c>
       <c r="N132" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>文</v>
       </c>
       <c r="O132" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌴文</v>
       </c>
       <c r="P132" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌴</v>
-      </c>
-    </row>
-    <row r="133" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌴p</v>
+      </c>
+      <c r="Q132" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌴&lt;rt&gt;&amp;#x202E;文&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R132" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌴q</v>
+      </c>
+    </row>
+    <row r="133" spans="2:18">
       <c r="B133" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D335</v>
       </c>
       <c r="C133" cm="1">
@@ -16827,7 +17875,7 @@
         <v>48</v>
       </c>
       <c r="F133" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌵</v>
       </c>
       <c r="H133" t="s">
@@ -16855,29 +17903,37 @@
         <v>8979</v>
       </c>
       <c r="L133" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>⚋𝌀⚊𝌀</v>
       </c>
       <c r="M133" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌵</v>
       </c>
       <c r="N133" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>禮</v>
       </c>
       <c r="O133" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌵禮</v>
       </c>
       <c r="P133" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌵</v>
-      </c>
-    </row>
-    <row r="134" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌵p</v>
+      </c>
+      <c r="Q133" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌵&lt;rt&gt;&amp;#x202E;禮&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R133" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌵q</v>
+      </c>
+    </row>
+    <row r="134" spans="2:18">
       <c r="B134" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D336</v>
       </c>
       <c r="C134" cm="1">
@@ -16891,7 +17947,7 @@
         <v>49</v>
       </c>
       <c r="F134" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌶</v>
       </c>
       <c r="H134" t="s">
@@ -16919,29 +17975,37 @@
         <v>8987</v>
       </c>
       <c r="L134" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>⚋𝌀⚋⚊</v>
       </c>
       <c r="M134" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌶</v>
       </c>
       <c r="N134" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>逃</v>
       </c>
       <c r="O134" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌶逃</v>
       </c>
       <c r="P134" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌶</v>
-      </c>
-    </row>
-    <row r="135" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌶p</v>
+      </c>
+      <c r="Q134" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌶&lt;rt&gt;&amp;#x202E;逃&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R134" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌶q</v>
+      </c>
+    </row>
+    <row r="135" spans="2:18">
       <c r="B135" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D337</v>
       </c>
       <c r="C135" cm="1">
@@ -16955,7 +18019,7 @@
         <v>50</v>
       </c>
       <c r="F135" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌷</v>
       </c>
       <c r="H135" t="s">
@@ -16983,29 +18047,37 @@
         <v>8988</v>
       </c>
       <c r="L135" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>⚋𝌀⚋⚋</v>
       </c>
       <c r="M135" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌷</v>
       </c>
       <c r="N135" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>唐</v>
       </c>
       <c r="O135" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌷唐</v>
       </c>
       <c r="P135" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌷</v>
-      </c>
-    </row>
-    <row r="136" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌷p</v>
+      </c>
+      <c r="Q135" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌷&lt;rt&gt;&amp;#x202E;唐&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R135" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌷q</v>
+      </c>
+    </row>
+    <row r="136" spans="2:18">
       <c r="B136" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D338</v>
       </c>
       <c r="C136" cm="1">
@@ -17019,7 +18091,7 @@
         <v>51</v>
       </c>
       <c r="F136" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌸</v>
       </c>
       <c r="H136" t="s">
@@ -17047,29 +18119,37 @@
         <v>8989</v>
       </c>
       <c r="L136" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>⚋𝌀⚋𝌀</v>
       </c>
       <c r="M136" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌸</v>
       </c>
       <c r="N136" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>常</v>
       </c>
       <c r="O136" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌸常</v>
       </c>
       <c r="P136" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌸</v>
-      </c>
-    </row>
-    <row r="137" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌸p</v>
+      </c>
+      <c r="Q136" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌸&lt;rt&gt;&amp;#x202E;常&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R136" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌸q</v>
+      </c>
+    </row>
+    <row r="137" spans="2:18">
       <c r="B137" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D339</v>
       </c>
       <c r="C137" cm="1">
@@ -17083,7 +18163,7 @@
         <v>52</v>
       </c>
       <c r="F137" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌹</v>
       </c>
       <c r="H137" t="s">
@@ -17111,29 +18191,37 @@
         <v>8997</v>
       </c>
       <c r="L137" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>⚋𝌀𝌀⚊</v>
       </c>
       <c r="M137" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌹</v>
       </c>
       <c r="N137" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>度</v>
       </c>
       <c r="O137" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌹度</v>
       </c>
       <c r="P137" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌹</v>
-      </c>
-    </row>
-    <row r="138" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌹p</v>
+      </c>
+      <c r="Q137" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌹&lt;rt&gt;&amp;#x202E;度&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R137" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌹q</v>
+      </c>
+    </row>
+    <row r="138" spans="2:18">
       <c r="B138" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D33A</v>
       </c>
       <c r="C138" cm="1">
@@ -17147,7 +18235,7 @@
         <v>53</v>
       </c>
       <c r="F138" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌺</v>
       </c>
       <c r="H138" t="s">
@@ -17175,29 +18263,37 @@
         <v>8998</v>
       </c>
       <c r="L138" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>⚋𝌀𝌀⚋</v>
       </c>
       <c r="M138" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌺</v>
       </c>
       <c r="N138" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>永</v>
       </c>
       <c r="O138" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌺永</v>
       </c>
       <c r="P138" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌺</v>
-      </c>
-    </row>
-    <row r="139" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌺p</v>
+      </c>
+      <c r="Q138" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌺&lt;rt&gt;&amp;#x202E;永&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R138" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌺q</v>
+      </c>
+    </row>
+    <row r="139" spans="2:18">
       <c r="B139" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D33B</v>
       </c>
       <c r="C139" cm="1">
@@ -17211,7 +18307,7 @@
         <v>54</v>
       </c>
       <c r="F139" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌻</v>
       </c>
       <c r="H139" t="s">
@@ -17239,29 +18335,37 @@
         <v>8999</v>
       </c>
       <c r="L139" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>⚋𝌀𝌀𝌀</v>
       </c>
       <c r="M139" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌻</v>
       </c>
       <c r="N139" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>昆</v>
       </c>
       <c r="O139" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌻昆</v>
       </c>
       <c r="P139" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌻</v>
-      </c>
-    </row>
-    <row r="140" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌻p</v>
+      </c>
+      <c r="Q139" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌻&lt;rt&gt;&amp;#x202E;昆&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R139" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌻q</v>
+      </c>
+    </row>
+    <row r="140" spans="2:18">
       <c r="B140" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D33C</v>
       </c>
       <c r="C140" cm="1">
@@ -17275,7 +18379,7 @@
         <v>55</v>
       </c>
       <c r="F140" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌼</v>
       </c>
       <c r="H140" t="s">
@@ -17303,29 +18407,37 @@
         <v>9777</v>
       </c>
       <c r="L140" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>𝌀⚊⚊⚊</v>
       </c>
       <c r="M140" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌼</v>
       </c>
       <c r="N140" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>減</v>
       </c>
       <c r="O140" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌼減</v>
       </c>
       <c r="P140" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌼</v>
-      </c>
-    </row>
-    <row r="141" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌼p</v>
+      </c>
+      <c r="Q140" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌼&lt;rt&gt;&amp;#x202E;減&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R140" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌼q</v>
+      </c>
+    </row>
+    <row r="141" spans="2:18">
       <c r="B141" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D33D</v>
       </c>
       <c r="C141" cm="1">
@@ -17339,7 +18451,7 @@
         <v>56</v>
       </c>
       <c r="F141" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌽</v>
       </c>
       <c r="H141" t="s">
@@ -17367,29 +18479,37 @@
         <v>9778</v>
       </c>
       <c r="L141" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>𝌀⚊⚊⚋</v>
       </c>
       <c r="M141" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌽</v>
       </c>
       <c r="N141" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>唫</v>
       </c>
       <c r="O141" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌽唫</v>
       </c>
       <c r="P141" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌽</v>
-      </c>
-    </row>
-    <row r="142" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌽p</v>
+      </c>
+      <c r="Q141" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌽&lt;rt&gt;&amp;#x202E;唫&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R141" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌽q</v>
+      </c>
+    </row>
+    <row r="142" spans="2:18">
       <c r="B142" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D33E</v>
       </c>
       <c r="C142" cm="1">
@@ -17403,7 +18523,7 @@
         <v>57</v>
       </c>
       <c r="F142" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌾</v>
       </c>
       <c r="H142" t="s">
@@ -17431,29 +18551,37 @@
         <v>9779</v>
       </c>
       <c r="L142" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>𝌀⚊⚊𝌀</v>
       </c>
       <c r="M142" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌾</v>
       </c>
       <c r="N142" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>守</v>
       </c>
       <c r="O142" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌾守</v>
       </c>
       <c r="P142" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌾</v>
-      </c>
-    </row>
-    <row r="143" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌾p</v>
+      </c>
+      <c r="Q142" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌾&lt;rt&gt;&amp;#x202E;守&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R142" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌾q</v>
+      </c>
+    </row>
+    <row r="143" spans="2:18">
       <c r="B143" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D33F</v>
       </c>
       <c r="C143" cm="1">
@@ -17467,7 +18595,7 @@
         <v>58</v>
       </c>
       <c r="F143" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝌿</v>
       </c>
       <c r="H143" t="s">
@@ -17495,29 +18623,37 @@
         <v>9787</v>
       </c>
       <c r="L143" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>𝌀⚊⚋⚊</v>
       </c>
       <c r="M143" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝌿</v>
       </c>
       <c r="N143" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>翕</v>
       </c>
       <c r="O143" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝌿翕</v>
       </c>
       <c r="P143" t="str">
-        <f t="shared" si="18"/>
-        <v>𝌿</v>
-      </c>
-    </row>
-    <row r="144" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝌿p</v>
+      </c>
+      <c r="Q143" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝌿&lt;rt&gt;&amp;#x202E;翕&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R143" t="str">
+        <f t="shared" si="30"/>
+        <v>𝌿q</v>
+      </c>
+    </row>
+    <row r="144" spans="2:18">
       <c r="B144" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D340</v>
       </c>
       <c r="C144" cm="1">
@@ -17531,7 +18667,7 @@
         <v>59</v>
       </c>
       <c r="F144" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍀</v>
       </c>
       <c r="H144" t="s">
@@ -17559,29 +18695,37 @@
         <v>9788</v>
       </c>
       <c r="L144" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>𝌀⚊⚋⚋</v>
       </c>
       <c r="M144" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝍀</v>
       </c>
       <c r="N144" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>聚</v>
       </c>
       <c r="O144" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍀聚</v>
       </c>
       <c r="P144" t="str">
-        <f t="shared" si="18"/>
-        <v>𝍀</v>
-      </c>
-    </row>
-    <row r="145" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍀p</v>
+      </c>
+      <c r="Q144" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍀&lt;rt&gt;&amp;#x202E;聚&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R144" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍀q</v>
+      </c>
+    </row>
+    <row r="145" spans="2:18">
       <c r="B145" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D341</v>
       </c>
       <c r="C145" cm="1">
@@ -17595,7 +18739,7 @@
         <v>60</v>
       </c>
       <c r="F145" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍁</v>
       </c>
       <c r="H145" t="s">
@@ -17623,29 +18767,37 @@
         <v>9789</v>
       </c>
       <c r="L145" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>𝌀⚊⚋𝌀</v>
       </c>
       <c r="M145" t="str">
-        <f t="shared" si="18"/>
+        <f t="shared" si="24"/>
         <v>𝍁</v>
       </c>
       <c r="N145" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>積</v>
       </c>
       <c r="O145" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍁積</v>
       </c>
       <c r="P145" t="str">
-        <f t="shared" si="18"/>
-        <v>𝍁</v>
-      </c>
-    </row>
-    <row r="146" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍁p</v>
+      </c>
+      <c r="Q145" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍁&lt;rt&gt;&amp;#x202E;積&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R145" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍁q</v>
+      </c>
+    </row>
+    <row r="146" spans="2:18">
       <c r="B146" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D342</v>
       </c>
       <c r="C146" cm="1">
@@ -17659,7 +18811,7 @@
         <v>61</v>
       </c>
       <c r="F146" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍂</v>
       </c>
       <c r="H146" t="s">
@@ -17687,29 +18839,37 @@
         <v>9797</v>
       </c>
       <c r="L146" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>𝌀⚊𝌀⚊</v>
       </c>
       <c r="M146" t="str">
-        <f t="shared" ref="M146:P161" si="22">_xlfn.UNICHAR($C146)</f>
+        <f t="shared" ref="M146:M161" si="31">_xlfn.UNICHAR($C146)</f>
         <v>𝍂</v>
       </c>
       <c r="N146" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>飾</v>
       </c>
       <c r="O146" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍂飾</v>
       </c>
       <c r="P146" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍂</v>
-      </c>
-    </row>
-    <row r="147" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍂p</v>
+      </c>
+      <c r="Q146" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍂&lt;rt&gt;&amp;#x202E;飾&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R146" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍂q</v>
+      </c>
+    </row>
+    <row r="147" spans="2:18">
       <c r="B147" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D343</v>
       </c>
       <c r="C147" cm="1">
@@ -17723,7 +18883,7 @@
         <v>62</v>
       </c>
       <c r="F147" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍃</v>
       </c>
       <c r="H147" t="s">
@@ -17751,29 +18911,37 @@
         <v>9798</v>
       </c>
       <c r="L147" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>𝌀⚊𝌀⚋</v>
       </c>
       <c r="M147" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍃</v>
       </c>
       <c r="N147" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>疑</v>
       </c>
       <c r="O147" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍃疑</v>
       </c>
       <c r="P147" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍃</v>
-      </c>
-    </row>
-    <row r="148" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍃p</v>
+      </c>
+      <c r="Q147" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍃&lt;rt&gt;&amp;#x202E;疑&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R147" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍃q</v>
+      </c>
+    </row>
+    <row r="148" spans="2:18">
       <c r="B148" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D344</v>
       </c>
       <c r="C148" cm="1">
@@ -17787,7 +18955,7 @@
         <v>63</v>
       </c>
       <c r="F148" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍄</v>
       </c>
       <c r="H148" t="s">
@@ -17815,29 +18983,37 @@
         <v>9799</v>
       </c>
       <c r="L148" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>𝌀⚊𝌀𝌀</v>
       </c>
       <c r="M148" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍄</v>
       </c>
       <c r="N148" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>視</v>
       </c>
       <c r="O148" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍄視</v>
       </c>
       <c r="P148" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍄</v>
-      </c>
-    </row>
-    <row r="149" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍄p</v>
+      </c>
+      <c r="Q148" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍄&lt;rt&gt;&amp;#x202E;視&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R148" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍄q</v>
+      </c>
+    </row>
+    <row r="149" spans="2:18">
       <c r="B149" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D345</v>
       </c>
       <c r="C149" cm="1">
@@ -17851,7 +19027,7 @@
         <v>64</v>
       </c>
       <c r="F149" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍅</v>
       </c>
       <c r="H149" t="s">
@@ -17879,29 +19055,37 @@
         <v>9877</v>
       </c>
       <c r="L149" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>𝌀⚋⚊⚊</v>
       </c>
       <c r="M149" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍅</v>
       </c>
       <c r="N149" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>沈</v>
       </c>
       <c r="O149" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍅沈</v>
       </c>
       <c r="P149" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍅</v>
-      </c>
-    </row>
-    <row r="150" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍅p</v>
+      </c>
+      <c r="Q149" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍅&lt;rt&gt;&amp;#x202E;沈&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R149" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍅q</v>
+      </c>
+    </row>
+    <row r="150" spans="2:18">
       <c r="B150" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D346</v>
       </c>
       <c r="C150" cm="1">
@@ -17915,7 +19099,7 @@
         <v>65</v>
       </c>
       <c r="F150" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍆</v>
       </c>
       <c r="H150" t="s">
@@ -17943,29 +19127,37 @@
         <v>9878</v>
       </c>
       <c r="L150" t="str">
-        <f t="shared" si="15"/>
+        <f t="shared" si="21"/>
         <v>𝌀⚋⚊⚋</v>
       </c>
       <c r="M150" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍆</v>
       </c>
       <c r="N150" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>內</v>
       </c>
       <c r="O150" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍆內</v>
       </c>
       <c r="P150" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍆</v>
-      </c>
-    </row>
-    <row r="151" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍆p</v>
+      </c>
+      <c r="Q150" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍆&lt;rt&gt;&amp;#x202E;內&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R150" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍆q</v>
+      </c>
+    </row>
+    <row r="151" spans="2:18">
       <c r="B151" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D347</v>
       </c>
       <c r="C151" cm="1">
@@ -17979,7 +19171,7 @@
         <v>66</v>
       </c>
       <c r="F151" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍇</v>
       </c>
       <c r="H151" t="s">
@@ -18007,29 +19199,37 @@
         <v>9879</v>
       </c>
       <c r="L151" t="str">
-        <f t="shared" ref="L151:L166" si="23">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J151,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
+        <f t="shared" ref="L151:L166" si="32">SUBSTITUTE(SUBSTITUTE(SUBSTITUTE(TEXT($J151,"0"),"1","⚊"),"2","⚋"),"3","𝌀")</f>
         <v>𝌀⚋⚊𝌀</v>
       </c>
       <c r="M151" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍇</v>
       </c>
       <c r="N151" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>去</v>
       </c>
       <c r="O151" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍇去</v>
       </c>
       <c r="P151" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍇</v>
-      </c>
-    </row>
-    <row r="152" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍇p</v>
+      </c>
+      <c r="Q151" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍇&lt;rt&gt;&amp;#x202E;去&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R151" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍇q</v>
+      </c>
+    </row>
+    <row r="152" spans="2:18">
       <c r="B152" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D348</v>
       </c>
       <c r="C152" cm="1">
@@ -18043,7 +19243,7 @@
         <v>67</v>
       </c>
       <c r="F152" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍈</v>
       </c>
       <c r="H152" t="s">
@@ -18071,29 +19271,37 @@
         <v>9887</v>
       </c>
       <c r="L152" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀⚋⚋⚊</v>
       </c>
       <c r="M152" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍈</v>
       </c>
       <c r="N152" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>晦</v>
       </c>
       <c r="O152" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍈晦</v>
       </c>
       <c r="P152" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍈</v>
-      </c>
-    </row>
-    <row r="153" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍈p</v>
+      </c>
+      <c r="Q152" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍈&lt;rt&gt;&amp;#x202E;晦&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R152" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍈q</v>
+      </c>
+    </row>
+    <row r="153" spans="2:18">
       <c r="B153" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D349</v>
       </c>
       <c r="C153" cm="1">
@@ -18107,7 +19315,7 @@
         <v>68</v>
       </c>
       <c r="F153" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍉</v>
       </c>
       <c r="H153" t="s">
@@ -18135,29 +19343,37 @@
         <v>9888</v>
       </c>
       <c r="L153" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀⚋⚋⚋</v>
       </c>
       <c r="M153" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍉</v>
       </c>
       <c r="N153" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>瞢</v>
       </c>
       <c r="O153" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍉瞢</v>
       </c>
       <c r="P153" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍉</v>
-      </c>
-    </row>
-    <row r="154" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍉p</v>
+      </c>
+      <c r="Q153" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍉&lt;rt&gt;&amp;#x202E;瞢&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R153" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍉q</v>
+      </c>
+    </row>
+    <row r="154" spans="2:18">
       <c r="B154" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D34A</v>
       </c>
       <c r="C154" cm="1">
@@ -18171,7 +19387,7 @@
         <v>69</v>
       </c>
       <c r="F154" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍊</v>
       </c>
       <c r="H154" t="s">
@@ -18199,29 +19415,37 @@
         <v>9889</v>
       </c>
       <c r="L154" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀⚋⚋𝌀</v>
       </c>
       <c r="M154" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍊</v>
       </c>
       <c r="N154" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>窮</v>
       </c>
       <c r="O154" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍊窮</v>
       </c>
       <c r="P154" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍊</v>
-      </c>
-    </row>
-    <row r="155" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍊p</v>
+      </c>
+      <c r="Q154" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍊&lt;rt&gt;&amp;#x202E;窮&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R154" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍊q</v>
+      </c>
+    </row>
+    <row r="155" spans="2:18">
       <c r="B155" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D34B</v>
       </c>
       <c r="C155" cm="1">
@@ -18235,7 +19459,7 @@
         <v>70</v>
       </c>
       <c r="F155" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍋</v>
       </c>
       <c r="H155" t="s">
@@ -18263,29 +19487,37 @@
         <v>9897</v>
       </c>
       <c r="L155" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀⚋𝌀⚊</v>
       </c>
       <c r="M155" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍋</v>
       </c>
       <c r="N155" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>割</v>
       </c>
       <c r="O155" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍋割</v>
       </c>
       <c r="P155" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍋</v>
-      </c>
-    </row>
-    <row r="156" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍋p</v>
+      </c>
+      <c r="Q155" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍋&lt;rt&gt;&amp;#x202E;割&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R155" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍋q</v>
+      </c>
+    </row>
+    <row r="156" spans="2:18">
       <c r="B156" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D34C</v>
       </c>
       <c r="C156" cm="1">
@@ -18299,7 +19531,7 @@
         <v>71</v>
       </c>
       <c r="F156" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍌</v>
       </c>
       <c r="H156" t="s">
@@ -18327,29 +19559,37 @@
         <v>9898</v>
       </c>
       <c r="L156" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀⚋𝌀⚋</v>
       </c>
       <c r="M156" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍌</v>
       </c>
       <c r="N156" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>止</v>
       </c>
       <c r="O156" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍌止</v>
       </c>
       <c r="P156" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍌</v>
-      </c>
-    </row>
-    <row r="157" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍌p</v>
+      </c>
+      <c r="Q156" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍌&lt;rt&gt;&amp;#x202E;止&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R156" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍌q</v>
+      </c>
+    </row>
+    <row r="157" spans="2:18">
       <c r="B157" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D34D</v>
       </c>
       <c r="C157" cm="1">
@@ -18363,7 +19603,7 @@
         <v>72</v>
       </c>
       <c r="F157" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍍</v>
       </c>
       <c r="H157" t="s">
@@ -18391,29 +19631,37 @@
         <v>9899</v>
       </c>
       <c r="L157" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀⚋𝌀𝌀</v>
       </c>
       <c r="M157" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍍</v>
       </c>
       <c r="N157" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>堅</v>
       </c>
       <c r="O157" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍍堅</v>
       </c>
       <c r="P157" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍍</v>
-      </c>
-    </row>
-    <row r="158" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍍p</v>
+      </c>
+      <c r="Q157" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍍&lt;rt&gt;&amp;#x202E;堅&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R157" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍍q</v>
+      </c>
+    </row>
+    <row r="158" spans="2:18">
       <c r="B158" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D34E</v>
       </c>
       <c r="C158" cm="1">
@@ -18427,7 +19675,7 @@
         <v>73</v>
       </c>
       <c r="F158" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍎</v>
       </c>
       <c r="H158" t="s">
@@ -18455,29 +19703,37 @@
         <v>9977</v>
       </c>
       <c r="L158" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀𝌀⚊⚊</v>
       </c>
       <c r="M158" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍎</v>
       </c>
       <c r="N158" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>成</v>
       </c>
       <c r="O158" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍎成</v>
       </c>
       <c r="P158" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍎</v>
-      </c>
-    </row>
-    <row r="159" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍎p</v>
+      </c>
+      <c r="Q158" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍎&lt;rt&gt;&amp;#x202E;成&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R158" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍎q</v>
+      </c>
+    </row>
+    <row r="159" spans="2:18">
       <c r="B159" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D34F</v>
       </c>
       <c r="C159" cm="1">
@@ -18491,7 +19747,7 @@
         <v>74</v>
       </c>
       <c r="F159" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍏</v>
       </c>
       <c r="H159" t="s">
@@ -18519,29 +19775,37 @@
         <v>9978</v>
       </c>
       <c r="L159" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀𝌀⚊⚋</v>
       </c>
       <c r="M159" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍏</v>
       </c>
       <c r="N159" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>䦯</v>
       </c>
       <c r="O159" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍏䦯</v>
       </c>
       <c r="P159" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍏</v>
-      </c>
-    </row>
-    <row r="160" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍏p</v>
+      </c>
+      <c r="Q159" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍏&lt;rt&gt;&amp;#x202E;䦯&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R159" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍏q</v>
+      </c>
+    </row>
+    <row r="160" spans="2:18">
       <c r="B160" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D350</v>
       </c>
       <c r="C160" cm="1">
@@ -18555,7 +19819,7 @@
         <v>75</v>
       </c>
       <c r="F160" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍐</v>
       </c>
       <c r="H160" t="s">
@@ -18583,29 +19847,37 @@
         <v>9979</v>
       </c>
       <c r="L160" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀𝌀⚊𝌀</v>
       </c>
       <c r="M160" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍐</v>
       </c>
       <c r="N160" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>失</v>
       </c>
       <c r="O160" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍐失</v>
       </c>
       <c r="P160" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍐</v>
-      </c>
-    </row>
-    <row r="161" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍐p</v>
+      </c>
+      <c r="Q160" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍐&lt;rt&gt;&amp;#x202E;失&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R160" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍐q</v>
+      </c>
+    </row>
+    <row r="161" spans="2:18">
       <c r="B161" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D351</v>
       </c>
       <c r="C161" cm="1">
@@ -18619,7 +19891,7 @@
         <v>76</v>
       </c>
       <c r="F161" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍑</v>
       </c>
       <c r="H161" t="s">
@@ -18647,29 +19919,37 @@
         <v>9987</v>
       </c>
       <c r="L161" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀𝌀⚋⚊</v>
       </c>
       <c r="M161" t="str">
-        <f t="shared" si="22"/>
+        <f t="shared" si="31"/>
         <v>𝍑</v>
       </c>
       <c r="N161" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>劇</v>
       </c>
       <c r="O161" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍑劇</v>
       </c>
       <c r="P161" t="str">
-        <f t="shared" si="22"/>
-        <v>𝍑</v>
-      </c>
-    </row>
-    <row r="162" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍑p</v>
+      </c>
+      <c r="Q161" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍑&lt;rt&gt;&amp;#x202E;劇&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R161" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍑q</v>
+      </c>
+    </row>
+    <row r="162" spans="2:18">
       <c r="B162" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D352</v>
       </c>
       <c r="C162" cm="1">
@@ -18683,7 +19963,7 @@
         <v>77</v>
       </c>
       <c r="F162" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍒</v>
       </c>
       <c r="H162" t="s">
@@ -18711,29 +19991,37 @@
         <v>9988</v>
       </c>
       <c r="L162" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀𝌀⚋⚋</v>
       </c>
       <c r="M162" t="str">
-        <f t="shared" ref="M162:P166" si="24">_xlfn.UNICHAR($C162)</f>
+        <f t="shared" ref="M162:M166" si="33">_xlfn.UNICHAR($C162)</f>
         <v>𝍒</v>
       </c>
       <c r="N162" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>馴</v>
       </c>
       <c r="O162" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍒馴</v>
       </c>
       <c r="P162" t="str">
-        <f t="shared" si="24"/>
-        <v>𝍒</v>
-      </c>
-    </row>
-    <row r="163" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍒p</v>
+      </c>
+      <c r="Q162" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍒&lt;rt&gt;&amp;#x202E;馴&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R162" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍒q</v>
+      </c>
+    </row>
+    <row r="163" spans="2:18">
       <c r="B163" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D353</v>
       </c>
       <c r="C163" cm="1">
@@ -18747,7 +20035,7 @@
         <v>78</v>
       </c>
       <c r="F163" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍓</v>
       </c>
       <c r="H163" t="s">
@@ -18775,29 +20063,37 @@
         <v>9989</v>
       </c>
       <c r="L163" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀𝌀⚋𝌀</v>
       </c>
       <c r="M163" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>𝍓</v>
       </c>
       <c r="N163" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>將</v>
       </c>
       <c r="O163" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍓將</v>
       </c>
       <c r="P163" t="str">
-        <f t="shared" si="24"/>
-        <v>𝍓</v>
-      </c>
-    </row>
-    <row r="164" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍓p</v>
+      </c>
+      <c r="Q163" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍓&lt;rt&gt;&amp;#x202E;將&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R163" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍓q</v>
+      </c>
+    </row>
+    <row r="164" spans="2:18">
       <c r="B164" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D354</v>
       </c>
       <c r="C164" cm="1">
@@ -18811,7 +20107,7 @@
         <v>79</v>
       </c>
       <c r="F164" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍔</v>
       </c>
       <c r="H164" t="s">
@@ -18839,29 +20135,37 @@
         <v>9997</v>
       </c>
       <c r="L164" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀𝌀𝌀⚊</v>
       </c>
       <c r="M164" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>𝍔</v>
       </c>
       <c r="N164" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>難</v>
       </c>
       <c r="O164" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍔難</v>
       </c>
       <c r="P164" t="str">
-        <f t="shared" si="24"/>
-        <v>𝍔</v>
-      </c>
-    </row>
-    <row r="165" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍔p</v>
+      </c>
+      <c r="Q164" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍔&lt;rt&gt;&amp;#x202E;難&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R164" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍔q</v>
+      </c>
+    </row>
+    <row r="165" spans="2:18">
       <c r="B165" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D355</v>
       </c>
       <c r="C165" cm="1">
@@ -18875,7 +20179,7 @@
         <v>80</v>
       </c>
       <c r="F165" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍕</v>
       </c>
       <c r="H165" t="s">
@@ -18903,29 +20207,37 @@
         <v>9998</v>
       </c>
       <c r="L165" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀𝌀𝌀⚋</v>
       </c>
       <c r="M165" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>𝍕</v>
       </c>
       <c r="N165" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>勤</v>
       </c>
       <c r="O165" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍕勤</v>
       </c>
       <c r="P165" t="str">
-        <f t="shared" si="24"/>
-        <v>𝍕</v>
-      </c>
-    </row>
-    <row r="166" spans="2:16">
+        <f t="shared" si="28"/>
+        <v>𝍕p</v>
+      </c>
+      <c r="Q165" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍕&lt;rt&gt;&amp;#x202E;勤&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R165" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍕q</v>
+      </c>
+    </row>
+    <row r="166" spans="2:18">
       <c r="B166" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="25"/>
         <v>1D356</v>
       </c>
       <c r="C166" cm="1">
@@ -18939,7 +20251,7 @@
         <v>81</v>
       </c>
       <c r="F166" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="8"/>
         <v>𝍖</v>
       </c>
       <c r="H166" t="s">
@@ -18967,24 +20279,32 @@
         <v>9999</v>
       </c>
       <c r="L166" t="str">
-        <f t="shared" si="23"/>
+        <f t="shared" si="32"/>
         <v>𝌀𝌀𝌀𝌀</v>
       </c>
       <c r="M166" t="str">
-        <f t="shared" si="24"/>
+        <f t="shared" si="33"/>
         <v>𝍖</v>
       </c>
       <c r="N166" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="26"/>
         <v>養</v>
       </c>
       <c r="O166" t="str">
-        <f t="shared" si="21"/>
+        <f t="shared" si="27"/>
         <v>𝍖養</v>
       </c>
       <c r="P166" t="str">
-        <f t="shared" si="24"/>
-        <v>𝍖</v>
+        <f t="shared" si="28"/>
+        <v>𝍖p</v>
+      </c>
+      <c r="Q166" t="str">
+        <f t="shared" si="29"/>
+        <v>&lt;ruby&gt;𝍖&lt;rt&gt;&amp;#x202E;養&amp;#x202C;&lt;/rt&gt;&lt;/ruby&gt;</v>
+      </c>
+      <c r="R166" t="str">
+        <f t="shared" si="30"/>
+        <v>𝍖q</v>
       </c>
     </row>
   </sheetData>
